--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2063,6 +2063,5867 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121597130</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>506703</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7053305</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121597364</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>506602</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7053286</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121598985</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>506335</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7053140</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121601957</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>506684</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7053378</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121597320</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>506606</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7053294</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121596987</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>506796</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7053411</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121596964</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>506818</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7053423</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121601347</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>506473</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7053383</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121599143</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>506325</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7053209</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121601665</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>506512</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7053384</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121601508</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>506490</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7053371</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121601916</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>506663</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7053393</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121601859</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>506600</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7053390</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121602116</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>506843</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7053491</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121597096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>506735</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7053336</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121597523</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>506599</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7053253</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121597940</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506473</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7053034</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121598549</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57509</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506432</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7053087</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121598902</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>506352</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7053112</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121597218</v>
+      </c>
+      <c r="B32" t="n">
+        <v>55958</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>506667</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7053309</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121597690</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>506558</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7053116</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121597673</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>506553</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7053113</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121597990</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79725</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>506470</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7053032</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121599094</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>506328</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7053195</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121599490</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>506379</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7053186</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121597978</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>506470</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7053032</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121597044</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>506743</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7053366</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121597382</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90716</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>506600</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7053289</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121598608</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>506426</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7053063</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121599680</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>506380</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7053232</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121597247</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90716</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>506669</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7053308</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121601872</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>506612</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7053395</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121601357</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57509</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>506460</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7053365</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121601171</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>506381</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7053357</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121597306</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>506628</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7053277</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121598953</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>506336</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7053124</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121598719</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>506374</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7053093</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121598834</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57509</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>506403</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7053127</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121598773</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>506378</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7053113</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121602039</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>506765</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7053438</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121598813</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90716</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>506403</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7053116</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121598801</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>506390</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7053088</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121597408</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91403</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>506592</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7053288</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121597797</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91403</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>506488</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7053023</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121601888</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>506625</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7053387</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597130</v>
+        <v>121601859</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,44 +2082,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506703</v>
+        <v>506600</v>
       </c>
       <c r="R13" t="n">
-        <v>7053305</v>
+        <v>7053390</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2180,12 +2170,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2203,10 +2193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597364</v>
+        <v>121601347</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2219,44 +2209,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506602</v>
+        <v>506473</v>
       </c>
       <c r="R14" t="n">
-        <v>7053286</v>
+        <v>7053383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2291,11 +2271,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2322,12 +2297,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2345,10 +2320,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121598985</v>
+        <v>121599094</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2361,44 +2336,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506335</v>
+        <v>506328</v>
       </c>
       <c r="R15" t="n">
-        <v>7053140</v>
+        <v>7053195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,22 +2419,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2482,10 +2452,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121601957</v>
+        <v>121597364</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2498,39 +2468,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506684</v>
+        <v>506602</v>
       </c>
       <c r="R16" t="n">
-        <v>7053378</v>
+        <v>7053286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2565,6 +2540,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2591,12 +2571,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2614,10 +2594,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597320</v>
+        <v>121596987</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2630,47 +2610,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506606</v>
+        <v>506796</v>
       </c>
       <c r="R17" t="n">
-        <v>7053294</v>
+        <v>7053411</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2702,11 +2672,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2733,12 +2698,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2756,7 +2721,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596987</v>
+        <v>121599143</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2792,17 +2757,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506796</v>
+        <v>506325</v>
       </c>
       <c r="R18" t="n">
-        <v>7053411</v>
+        <v>7053209</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2883,10 +2848,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596964</v>
+        <v>121597218</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>55958</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2899,21 +2864,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2923,10 +2888,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506818</v>
+        <v>506667</v>
       </c>
       <c r="R19" t="n">
-        <v>7053423</v>
+        <v>7053309</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,31 +2934,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3010,10 +2950,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121601347</v>
+        <v>121597044</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3022,38 +2962,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506473</v>
+        <v>506743</v>
       </c>
       <c r="R20" t="n">
-        <v>7053383</v>
+        <v>7053366</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3096,31 +3036,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3137,10 +3052,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121599143</v>
+        <v>121598902</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3153,34 +3068,44 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506325</v>
+        <v>506352</v>
       </c>
       <c r="R21" t="n">
-        <v>7053209</v>
+        <v>7053112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3241,12 +3166,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3264,10 +3189,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121601665</v>
+        <v>121598813</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3280,34 +3205,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506512</v>
+        <v>506403</v>
       </c>
       <c r="R22" t="n">
-        <v>7053384</v>
+        <v>7053116</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3368,12 +3307,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3391,10 +3330,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601508</v>
+        <v>121598834</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3407,34 +3346,53 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506490</v>
+        <v>506403</v>
       </c>
       <c r="R23" t="n">
-        <v>7053371</v>
+        <v>7053127</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3481,26 +3439,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3518,7 +3456,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601916</v>
+        <v>121602039</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -3558,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506663</v>
+        <v>506765</v>
       </c>
       <c r="R24" t="n">
-        <v>7053393</v>
+        <v>7053438</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3594,11 +3532,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3650,10 +3583,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121601859</v>
+        <v>121597978</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3662,38 +3595,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506600</v>
+        <v>506470</v>
       </c>
       <c r="R25" t="n">
-        <v>7053390</v>
+        <v>7053032</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3744,22 +3682,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3777,10 +3715,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121602116</v>
+        <v>121599490</v>
       </c>
       <c r="B26" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3793,39 +3731,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506843</v>
+        <v>506379</v>
       </c>
       <c r="R26" t="n">
-        <v>7053491</v>
+        <v>7053186</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3876,22 +3814,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3909,10 +3847,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597096</v>
+        <v>121601916</v>
       </c>
       <c r="B27" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3925,39 +3863,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506735</v>
+        <v>506663</v>
       </c>
       <c r="R27" t="n">
-        <v>7053336</v>
+        <v>7053393</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3992,6 +3925,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4018,12 +3956,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4041,10 +3979,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597523</v>
+        <v>121601508</v>
       </c>
       <c r="B28" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4057,39 +3995,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506599</v>
+        <v>506490</v>
       </c>
       <c r="R28" t="n">
-        <v>7053253</v>
+        <v>7053371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4150,12 +4083,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4173,10 +4106,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597940</v>
+        <v>121597408</v>
       </c>
       <c r="B29" t="n">
-        <v>79690</v>
+        <v>91403</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4185,38 +4118,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506473</v>
+        <v>506592</v>
       </c>
       <c r="R29" t="n">
-        <v>7053034</v>
+        <v>7053288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4267,22 +4205,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4300,10 +4238,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121598549</v>
+        <v>121597673</v>
       </c>
       <c r="B30" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4316,31 +4254,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4354,13 +4288,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506432</v>
+        <v>506553</v>
       </c>
       <c r="R30" t="n">
-        <v>7053087</v>
+        <v>7053113</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4404,6 +4338,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4421,10 +4375,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121598902</v>
+        <v>121597990</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>79725</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4433,48 +4387,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506352</v>
+        <v>506470</v>
       </c>
       <c r="R31" t="n">
-        <v>7053112</v>
+        <v>7053032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4525,22 +4474,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4558,10 +4507,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597218</v>
+        <v>121601872</v>
       </c>
       <c r="B32" t="n">
-        <v>55958</v>
+        <v>57372</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4574,34 +4523,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506667</v>
+        <v>506612</v>
       </c>
       <c r="R32" t="n">
-        <v>7053309</v>
+        <v>7053395</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4644,6 +4598,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4660,7 +4639,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597690</v>
+        <v>121598985</v>
       </c>
       <c r="B33" t="n">
         <v>57372</v>
@@ -4710,10 +4689,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506558</v>
+        <v>506335</v>
       </c>
       <c r="R33" t="n">
-        <v>7053116</v>
+        <v>7053140</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4774,12 +4753,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4797,7 +4776,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597673</v>
+        <v>121598719</v>
       </c>
       <c r="B34" t="n">
         <v>57372</v>
@@ -4833,7 +4812,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4847,10 +4826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506553</v>
+        <v>506374</v>
       </c>
       <c r="R34" t="n">
-        <v>7053113</v>
+        <v>7053093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4911,12 +4890,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4934,10 +4913,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597990</v>
+        <v>121597940</v>
       </c>
       <c r="B35" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4946,43 +4925,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506470</v>
+        <v>506473</v>
       </c>
       <c r="R35" t="n">
-        <v>7053032</v>
+        <v>7053034</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5066,10 +5040,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121599094</v>
+        <v>121597320</v>
       </c>
       <c r="B36" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5082,39 +5056,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506328</v>
+        <v>506606</v>
       </c>
       <c r="R36" t="n">
-        <v>7053195</v>
+        <v>7053294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5149,6 +5128,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5165,22 +5149,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5198,10 +5182,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121599490</v>
+        <v>121602116</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5214,39 +5198,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506379</v>
+        <v>506843</v>
       </c>
       <c r="R37" t="n">
-        <v>7053186</v>
+        <v>7053491</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5297,22 +5281,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5330,10 +5314,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597978</v>
+        <v>121601665</v>
       </c>
       <c r="B38" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5342,43 +5326,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506470</v>
+        <v>506512</v>
       </c>
       <c r="R38" t="n">
-        <v>7053032</v>
+        <v>7053384</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5429,22 +5408,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5462,10 +5441,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121597044</v>
+        <v>121597096</v>
       </c>
       <c r="B39" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5474,38 +5453,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506743</v>
+        <v>506735</v>
       </c>
       <c r="R39" t="n">
-        <v>7053366</v>
+        <v>7053336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5548,6 +5532,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5564,10 +5573,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597382</v>
+        <v>121596964</v>
       </c>
       <c r="B40" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5580,39 +5589,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506600</v>
+        <v>506818</v>
       </c>
       <c r="R40" t="n">
-        <v>7053289</v>
+        <v>7053423</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5673,12 +5677,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5696,10 +5700,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598608</v>
+        <v>121599680</v>
       </c>
       <c r="B41" t="n">
-        <v>97059</v>
+        <v>79719</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5712,32 +5716,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5746,10 +5745,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506426</v>
+        <v>506380</v>
       </c>
       <c r="R41" t="n">
-        <v>7053063</v>
+        <v>7053232</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5784,11 +5783,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5801,6 +5795,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5818,10 +5832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121599680</v>
+        <v>121598608</v>
       </c>
       <c r="B42" t="n">
-        <v>79719</v>
+        <v>97059</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5834,27 +5848,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5863,10 +5882,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506380</v>
+        <v>506426</v>
       </c>
       <c r="R42" t="n">
-        <v>7053232</v>
+        <v>7053063</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5901,6 +5920,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5913,26 +5937,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5950,10 +5954,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121597247</v>
+        <v>121598549</v>
       </c>
       <c r="B43" t="n">
-        <v>90716</v>
+        <v>57509</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5966,42 +5970,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506669</v>
+        <v>506432</v>
       </c>
       <c r="R43" t="n">
-        <v>7053308</v>
+        <v>7053087</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6045,26 +6058,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6082,10 +6075,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121601872</v>
+        <v>121598953</v>
       </c>
       <c r="B44" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6098,39 +6091,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506612</v>
+        <v>506336</v>
       </c>
       <c r="R44" t="n">
-        <v>7053395</v>
+        <v>7053124</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6191,12 +6184,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6214,10 +6207,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121601357</v>
+        <v>121597247</v>
       </c>
       <c r="B45" t="n">
-        <v>57509</v>
+        <v>90716</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6230,51 +6223,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506460</v>
+        <v>506669</v>
       </c>
       <c r="R45" t="n">
-        <v>7053365</v>
+        <v>7053308</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6318,6 +6302,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6467,10 +6471,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121597306</v>
+        <v>121601888</v>
       </c>
       <c r="B47" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6483,44 +6487,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506628</v>
+        <v>506625</v>
       </c>
       <c r="R47" t="n">
-        <v>7053277</v>
+        <v>7053387</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6555,11 +6549,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6586,12 +6575,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6609,10 +6598,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121598953</v>
+        <v>121597130</v>
       </c>
       <c r="B48" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6625,39 +6614,44 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506336</v>
+        <v>506703</v>
       </c>
       <c r="R48" t="n">
-        <v>7053124</v>
+        <v>7053305</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6718,12 +6712,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6741,7 +6735,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598719</v>
+        <v>121598801</v>
       </c>
       <c r="B49" t="n">
         <v>57372</v>
@@ -6780,21 +6774,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506374</v>
+        <v>506390</v>
       </c>
       <c r="R49" t="n">
-        <v>7053093</v>
+        <v>7053088</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6878,10 +6867,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598834</v>
+        <v>121598773</v>
       </c>
       <c r="B50" t="n">
-        <v>57509</v>
+        <v>90720</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6894,53 +6883,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506403</v>
+        <v>506378</v>
       </c>
       <c r="R50" t="n">
-        <v>7053127</v>
+        <v>7053113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6987,6 +6962,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7004,10 +6999,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121598773</v>
+        <v>121597382</v>
       </c>
       <c r="B51" t="n">
-        <v>90720</v>
+        <v>90716</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7020,21 +7015,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7045,14 +7040,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506378</v>
+        <v>506600</v>
       </c>
       <c r="R51" t="n">
-        <v>7053113</v>
+        <v>7053289</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7113,12 +7108,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7136,10 +7131,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121602039</v>
+        <v>121597306</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7152,34 +7147,44 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506765</v>
+        <v>506628</v>
       </c>
       <c r="R52" t="n">
-        <v>7053438</v>
+        <v>7053277</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7214,6 +7219,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7240,12 +7250,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7263,10 +7273,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121598813</v>
+        <v>121597797</v>
       </c>
       <c r="B53" t="n">
-        <v>90716</v>
+        <v>91403</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7275,37 +7285,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -7313,14 +7314,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506403</v>
+        <v>506488</v>
       </c>
       <c r="R53" t="n">
-        <v>7053116</v>
+        <v>7053023</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7404,10 +7405,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121598801</v>
+        <v>121601957</v>
       </c>
       <c r="B54" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7420,39 +7421,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506390</v>
+        <v>506684</v>
       </c>
       <c r="R54" t="n">
-        <v>7053088</v>
+        <v>7053378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7513,12 +7514,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7536,10 +7537,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121597408</v>
+        <v>121597523</v>
       </c>
       <c r="B55" t="n">
-        <v>91403</v>
+        <v>90738</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7548,25 +7549,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7581,10 +7582,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506592</v>
+        <v>506599</v>
       </c>
       <c r="R55" t="n">
-        <v>7053288</v>
+        <v>7053253</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7645,12 +7646,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7668,10 +7669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121597797</v>
+        <v>121601357</v>
       </c>
       <c r="B56" t="n">
-        <v>91403</v>
+        <v>57509</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7680,46 +7681,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506488</v>
+        <v>506460</v>
       </c>
       <c r="R56" t="n">
-        <v>7053023</v>
+        <v>7053365</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7763,26 +7773,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7800,10 +7790,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121601888</v>
+        <v>121597690</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7816,34 +7806,44 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506625</v>
+        <v>506558</v>
       </c>
       <c r="R57" t="n">
-        <v>7053387</v>
+        <v>7053116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7904,12 +7904,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121601859</v>
+        <v>121597940</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,21 +2082,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506600</v>
+        <v>506473</v>
       </c>
       <c r="R13" t="n">
-        <v>7053390</v>
+        <v>7053034</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2160,22 +2160,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121601347</v>
+        <v>121599490</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2209,34 +2209,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506473</v>
+        <v>506379</v>
       </c>
       <c r="R14" t="n">
-        <v>7053383</v>
+        <v>7053186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,22 +2292,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121599094</v>
+        <v>121598773</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2336,27 +2341,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2365,10 +2370,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506328</v>
+        <v>506378</v>
       </c>
       <c r="R15" t="n">
-        <v>7053195</v>
+        <v>7053113</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2419,22 +2424,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2452,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597364</v>
+        <v>121598985</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2468,16 +2473,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506602</v>
+        <v>506335</v>
       </c>
       <c r="R16" t="n">
-        <v>7053286</v>
+        <v>7053140</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,11 +2545,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596987</v>
+        <v>121599094</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2610,37 +2610,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506796</v>
+        <v>506328</v>
       </c>
       <c r="R17" t="n">
-        <v>7053411</v>
+        <v>7053195</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2688,22 +2693,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2721,7 +2726,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121599143</v>
+        <v>121601508</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2757,14 +2762,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506325</v>
+        <v>506490</v>
       </c>
       <c r="R18" t="n">
-        <v>7053209</v>
+        <v>7053371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2848,10 +2853,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597218</v>
+        <v>121597673</v>
       </c>
       <c r="B19" t="n">
-        <v>55958</v>
+        <v>57372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2864,34 +2869,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506667</v>
+        <v>506553</v>
       </c>
       <c r="R19" t="n">
-        <v>7053309</v>
+        <v>7053113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2934,6 +2949,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2950,10 +2990,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597044</v>
+        <v>121597306</v>
       </c>
       <c r="B20" t="n">
-        <v>97059</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2962,38 +3002,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506743</v>
+        <v>506628</v>
       </c>
       <c r="R20" t="n">
-        <v>7053366</v>
+        <v>7053277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3028,6 +3078,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3036,6 +3091,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3052,10 +3132,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121598902</v>
+        <v>121596987</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3068,47 +3148,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506352</v>
+        <v>506796</v>
       </c>
       <c r="R21" t="n">
-        <v>7053112</v>
+        <v>7053411</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3166,12 +3236,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3189,7 +3259,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598813</v>
+        <v>121597247</v>
       </c>
       <c r="B22" t="n">
         <v>90716</v>
@@ -3222,16 +3292,7 @@
           <t>(Fr.) Krieglst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3239,14 +3300,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506403</v>
+        <v>506669</v>
       </c>
       <c r="R22" t="n">
-        <v>7053116</v>
+        <v>7053308</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3307,12 +3368,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3330,10 +3391,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121598834</v>
+        <v>121601171</v>
       </c>
       <c r="B23" t="n">
-        <v>57509</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3346,53 +3407,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506403</v>
+        <v>506381</v>
       </c>
       <c r="R23" t="n">
-        <v>7053127</v>
+        <v>7053357</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3439,6 +3486,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3456,10 +3523,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121602039</v>
+        <v>121601957</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,34 +3539,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506765</v>
+        <v>506684</v>
       </c>
       <c r="R24" t="n">
-        <v>7053438</v>
+        <v>7053378</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3560,12 +3632,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3583,10 +3655,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597978</v>
+        <v>121597044</v>
       </c>
       <c r="B25" t="n">
-        <v>79719</v>
+        <v>97059</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3599,39 +3671,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506470</v>
+        <v>506743</v>
       </c>
       <c r="R25" t="n">
-        <v>7053032</v>
+        <v>7053366</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3674,31 +3741,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3715,10 +3757,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121599490</v>
+        <v>121601872</v>
       </c>
       <c r="B26" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3731,39 +3773,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506379</v>
+        <v>506612</v>
       </c>
       <c r="R26" t="n">
-        <v>7053186</v>
+        <v>7053395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3814,22 +3856,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3847,10 +3889,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121601916</v>
+        <v>121598902</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3863,34 +3905,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506663</v>
+        <v>506352</v>
       </c>
       <c r="R27" t="n">
-        <v>7053393</v>
+        <v>7053112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3925,11 +3977,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3956,12 +4003,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3979,7 +4026,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601508</v>
+        <v>121601347</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -4015,14 +4062,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506490</v>
+        <v>506473</v>
       </c>
       <c r="R28" t="n">
-        <v>7053371</v>
+        <v>7053383</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4106,10 +4153,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597408</v>
+        <v>121598813</v>
       </c>
       <c r="B29" t="n">
-        <v>91403</v>
+        <v>90716</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4118,28 +4165,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4147,14 +4203,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506592</v>
+        <v>506403</v>
       </c>
       <c r="R29" t="n">
-        <v>7053288</v>
+        <v>7053116</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4215,12 +4271,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4238,10 +4294,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597673</v>
+        <v>121598953</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4254,44 +4310,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506553</v>
+        <v>506336</v>
       </c>
       <c r="R30" t="n">
-        <v>7053113</v>
+        <v>7053124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4352,12 +4403,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4375,10 +4426,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597990</v>
+        <v>121597690</v>
       </c>
       <c r="B31" t="n">
-        <v>79725</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4387,43 +4438,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506470</v>
+        <v>506558</v>
       </c>
       <c r="R31" t="n">
-        <v>7053032</v>
+        <v>7053116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4474,22 +4530,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4507,10 +4563,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121601872</v>
+        <v>121599680</v>
       </c>
       <c r="B32" t="n">
-        <v>57372</v>
+        <v>79719</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4519,43 +4575,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506612</v>
+        <v>506380</v>
       </c>
       <c r="R32" t="n">
-        <v>7053395</v>
+        <v>7053232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4606,22 +4662,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4639,10 +4695,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121598985</v>
+        <v>121602039</v>
       </c>
       <c r="B33" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4655,44 +4711,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506335</v>
+        <v>506765</v>
       </c>
       <c r="R33" t="n">
-        <v>7053140</v>
+        <v>7053438</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4753,12 +4799,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4776,7 +4822,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121598719</v>
+        <v>121597130</v>
       </c>
       <c r="B34" t="n">
         <v>57372</v>
@@ -4812,7 +4858,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4822,14 +4868,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506374</v>
+        <v>506703</v>
       </c>
       <c r="R34" t="n">
-        <v>7053093</v>
+        <v>7053305</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4890,12 +4936,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4913,10 +4959,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597940</v>
+        <v>121597978</v>
       </c>
       <c r="B35" t="n">
-        <v>79690</v>
+        <v>79719</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4925,38 +4971,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506473</v>
+        <v>506470</v>
       </c>
       <c r="R35" t="n">
-        <v>7053034</v>
+        <v>7053032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5040,10 +5091,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597320</v>
+        <v>121597096</v>
       </c>
       <c r="B36" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5056,44 +5107,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506606</v>
+        <v>506735</v>
       </c>
       <c r="R36" t="n">
-        <v>7053294</v>
+        <v>7053336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5128,11 +5174,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5159,12 +5200,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5182,10 +5223,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121602116</v>
+        <v>121597523</v>
       </c>
       <c r="B37" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5198,21 +5239,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5227,10 +5268,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506843</v>
+        <v>506599</v>
       </c>
       <c r="R37" t="n">
-        <v>7053491</v>
+        <v>7053253</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5314,7 +5355,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601665</v>
+        <v>121601916</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -5354,10 +5395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506512</v>
+        <v>506663</v>
       </c>
       <c r="R38" t="n">
-        <v>7053384</v>
+        <v>7053393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5390,6 +5431,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5441,10 +5487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121597096</v>
+        <v>121601859</v>
       </c>
       <c r="B39" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5457,39 +5503,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506735</v>
+        <v>506600</v>
       </c>
       <c r="R39" t="n">
-        <v>7053336</v>
+        <v>7053390</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5550,12 +5591,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5573,10 +5614,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121596964</v>
+        <v>121598608</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5585,38 +5626,48 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506818</v>
+        <v>506426</v>
       </c>
       <c r="R40" t="n">
-        <v>7053423</v>
+        <v>7053063</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5651,6 +5702,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5663,26 +5719,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5700,10 +5736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121599680</v>
+        <v>121598834</v>
       </c>
       <c r="B41" t="n">
-        <v>79719</v>
+        <v>57509</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5712,43 +5748,57 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506380</v>
+        <v>506403</v>
       </c>
       <c r="R41" t="n">
-        <v>7053232</v>
+        <v>7053127</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5795,26 +5845,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5832,10 +5862,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121598608</v>
+        <v>121602116</v>
       </c>
       <c r="B42" t="n">
-        <v>97059</v>
+        <v>90720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5844,48 +5874,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506426</v>
+        <v>506843</v>
       </c>
       <c r="R42" t="n">
-        <v>7053063</v>
+        <v>7053491</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5920,11 +5945,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5937,6 +5957,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5954,10 +5994,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121598549</v>
+        <v>121597408</v>
       </c>
       <c r="B43" t="n">
-        <v>57509</v>
+        <v>91403</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5966,55 +6006,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506432</v>
+        <v>506592</v>
       </c>
       <c r="R43" t="n">
-        <v>7053087</v>
+        <v>7053288</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6058,6 +6089,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6075,10 +6126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598953</v>
+        <v>121598719</v>
       </c>
       <c r="B44" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6091,39 +6142,44 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506336</v>
+        <v>506374</v>
       </c>
       <c r="R44" t="n">
-        <v>7053124</v>
+        <v>7053093</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6184,12 +6240,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6207,10 +6263,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121597247</v>
+        <v>121597990</v>
       </c>
       <c r="B45" t="n">
-        <v>90716</v>
+        <v>79725</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6219,31 +6275,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6252,10 +6308,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506669</v>
+        <v>506470</v>
       </c>
       <c r="R45" t="n">
-        <v>7053308</v>
+        <v>7053032</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6306,22 +6362,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6339,10 +6395,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601171</v>
+        <v>121597382</v>
       </c>
       <c r="B46" t="n">
-        <v>90720</v>
+        <v>90716</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6355,21 +6411,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6380,14 +6436,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506381</v>
+        <v>506600</v>
       </c>
       <c r="R46" t="n">
-        <v>7053357</v>
+        <v>7053289</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6448,12 +6504,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6471,7 +6527,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601888</v>
+        <v>121599143</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -6507,14 +6563,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506625</v>
+        <v>506325</v>
       </c>
       <c r="R47" t="n">
-        <v>7053387</v>
+        <v>7053209</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6598,10 +6654,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121597130</v>
+        <v>121601665</v>
       </c>
       <c r="B48" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6614,44 +6670,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506703</v>
+        <v>506512</v>
       </c>
       <c r="R48" t="n">
-        <v>7053305</v>
+        <v>7053384</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6712,12 +6758,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6735,10 +6781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598801</v>
+        <v>121597797</v>
       </c>
       <c r="B49" t="n">
-        <v>57372</v>
+        <v>91403</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6747,43 +6793,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506390</v>
+        <v>506488</v>
       </c>
       <c r="R49" t="n">
-        <v>7053088</v>
+        <v>7053023</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6867,10 +6913,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598773</v>
+        <v>121597320</v>
       </c>
       <c r="B50" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6883,39 +6929,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506378</v>
+        <v>506606</v>
       </c>
       <c r="R50" t="n">
-        <v>7053113</v>
+        <v>7053294</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6950,6 +7001,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6976,12 +7032,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6999,10 +7055,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121597382</v>
+        <v>121596964</v>
       </c>
       <c r="B51" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7015,39 +7071,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506600</v>
+        <v>506818</v>
       </c>
       <c r="R51" t="n">
-        <v>7053289</v>
+        <v>7053423</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7108,12 +7159,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7131,10 +7182,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121597306</v>
+        <v>121598801</v>
       </c>
       <c r="B52" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7147,16 +7198,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7167,24 +7218,19 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506628</v>
+        <v>506390</v>
       </c>
       <c r="R52" t="n">
-        <v>7053277</v>
+        <v>7053088</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7219,11 +7265,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7250,12 +7291,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7273,10 +7314,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121597797</v>
+        <v>121598549</v>
       </c>
       <c r="B53" t="n">
-        <v>91403</v>
+        <v>57509</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7285,46 +7326,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506488</v>
+        <v>506432</v>
       </c>
       <c r="R53" t="n">
-        <v>7053023</v>
+        <v>7053087</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7368,26 +7418,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7405,10 +7435,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121601957</v>
+        <v>121601357</v>
       </c>
       <c r="B54" t="n">
-        <v>90720</v>
+        <v>57509</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7421,42 +7451,51 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506684</v>
+        <v>506460</v>
       </c>
       <c r="R54" t="n">
-        <v>7053378</v>
+        <v>7053365</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7500,26 +7539,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7537,10 +7556,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121597523</v>
+        <v>121601888</v>
       </c>
       <c r="B55" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7553,39 +7572,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506599</v>
+        <v>506625</v>
       </c>
       <c r="R55" t="n">
-        <v>7053253</v>
+        <v>7053387</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7646,12 +7660,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7669,10 +7683,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121601357</v>
+        <v>121597218</v>
       </c>
       <c r="B56" t="n">
-        <v>57509</v>
+        <v>55958</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7685,51 +7699,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506460</v>
+        <v>506667</v>
       </c>
       <c r="R56" t="n">
-        <v>7053365</v>
+        <v>7053309</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7769,11 +7777,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7790,10 +7793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121597690</v>
+        <v>121597364</v>
       </c>
       <c r="B57" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7806,16 +7809,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7824,6 +7827,8 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -7840,10 +7845,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506558</v>
+        <v>506602</v>
       </c>
       <c r="R57" t="n">
-        <v>7053116</v>
+        <v>7053286</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7878,6 +7883,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7890,6 +7900,11 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597940</v>
+        <v>121597523</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>90738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,34 +2082,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506473</v>
+        <v>506599</v>
       </c>
       <c r="R13" t="n">
-        <v>7053034</v>
+        <v>7053253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2160,22 +2165,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2193,10 +2198,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121599490</v>
+        <v>121598608</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>97059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2205,31 +2210,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2238,10 +2248,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506379</v>
+        <v>506426</v>
       </c>
       <c r="R14" t="n">
-        <v>7053186</v>
+        <v>7053063</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,6 +2286,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2288,26 +2303,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121598773</v>
+        <v>121597673</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2341,36 +2336,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506378</v>
+        <v>506553</v>
       </c>
       <c r="R15" t="n">
         <v>7053113</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121598985</v>
+        <v>121597130</v>
       </c>
       <c r="B16" t="n">
         <v>57372</v>
@@ -2493,7 +2493,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506335</v>
+        <v>506703</v>
       </c>
       <c r="R16" t="n">
-        <v>7053140</v>
+        <v>7053305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121601508</v>
+        <v>121597990</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>79725</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2760,16 +2760,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506490</v>
+        <v>506470</v>
       </c>
       <c r="R18" t="n">
-        <v>7053371</v>
+        <v>7053032</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2820,22 +2825,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2853,10 +2858,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597673</v>
+        <v>121597306</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2869,16 +2874,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2899,14 +2904,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506553</v>
+        <v>506628</v>
       </c>
       <c r="R19" t="n">
-        <v>7053113</v>
+        <v>7053277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2939,6 +2944,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2990,10 +3000,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597306</v>
+        <v>121598813</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3006,44 +3016,48 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506628</v>
+        <v>506403</v>
       </c>
       <c r="R20" t="n">
-        <v>7053277</v>
+        <v>7053116</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,11 +3092,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3109,12 +3118,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3132,10 +3141,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121596987</v>
+        <v>121597978</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3144,41 +3153,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506796</v>
+        <v>506470</v>
       </c>
       <c r="R21" t="n">
-        <v>7053411</v>
+        <v>7053032</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3226,22 +3240,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3259,10 +3273,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597247</v>
+        <v>121597320</v>
       </c>
       <c r="B22" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3275,39 +3289,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506669</v>
+        <v>506606</v>
       </c>
       <c r="R22" t="n">
-        <v>7053308</v>
+        <v>7053294</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3342,6 +3361,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3368,12 +3392,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3391,10 +3415,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601171</v>
+        <v>121601665</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3407,39 +3431,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506381</v>
+        <v>506512</v>
       </c>
       <c r="R23" t="n">
-        <v>7053357</v>
+        <v>7053384</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3500,12 +3519,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3523,10 +3542,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601957</v>
+        <v>121602039</v>
       </c>
       <c r="B24" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3539,39 +3558,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506684</v>
+        <v>506765</v>
       </c>
       <c r="R24" t="n">
-        <v>7053378</v>
+        <v>7053438</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3632,12 +3646,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3655,10 +3669,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597044</v>
+        <v>121598985</v>
       </c>
       <c r="B25" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3667,38 +3681,48 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506743</v>
+        <v>506335</v>
       </c>
       <c r="R25" t="n">
-        <v>7053366</v>
+        <v>7053140</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3741,6 +3765,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3757,10 +3806,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601872</v>
+        <v>121602116</v>
       </c>
       <c r="B26" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3773,39 +3822,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506612</v>
+        <v>506843</v>
       </c>
       <c r="R26" t="n">
-        <v>7053395</v>
+        <v>7053491</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3866,12 +3915,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3889,10 +3938,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121598902</v>
+        <v>121598773</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3905,44 +3954,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506352</v>
+        <v>506378</v>
       </c>
       <c r="R27" t="n">
-        <v>7053112</v>
+        <v>7053113</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4003,12 +4047,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4026,10 +4070,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601347</v>
+        <v>121601872</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4042,34 +4086,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506473</v>
+        <v>506612</v>
       </c>
       <c r="R28" t="n">
-        <v>7053383</v>
+        <v>7053395</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4130,12 +4179,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4153,10 +4202,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121598813</v>
+        <v>121601916</v>
       </c>
       <c r="B29" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4169,48 +4218,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506403</v>
+        <v>506663</v>
       </c>
       <c r="R29" t="n">
-        <v>7053116</v>
+        <v>7053393</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4245,6 +4280,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4271,12 +4311,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4294,10 +4334,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121598953</v>
+        <v>121597690</v>
       </c>
       <c r="B30" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4310,39 +4350,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506336</v>
+        <v>506558</v>
       </c>
       <c r="R30" t="n">
-        <v>7053124</v>
+        <v>7053116</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4403,12 +4448,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4426,10 +4471,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597690</v>
+        <v>121599680</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>79719</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4438,48 +4483,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506558</v>
+        <v>506380</v>
       </c>
       <c r="R31" t="n">
-        <v>7053116</v>
+        <v>7053232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4530,22 +4570,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4563,10 +4603,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121599680</v>
+        <v>121597797</v>
       </c>
       <c r="B32" t="n">
-        <v>79719</v>
+        <v>91403</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4579,39 +4619,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506380</v>
+        <v>506488</v>
       </c>
       <c r="R32" t="n">
-        <v>7053232</v>
+        <v>7053023</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4662,22 +4702,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4695,7 +4735,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121602039</v>
+        <v>121599143</v>
       </c>
       <c r="B33" t="n">
         <v>78609</v>
@@ -4731,14 +4771,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506765</v>
+        <v>506325</v>
       </c>
       <c r="R33" t="n">
-        <v>7053438</v>
+        <v>7053209</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4822,7 +4862,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597130</v>
+        <v>121598902</v>
       </c>
       <c r="B34" t="n">
         <v>57372</v>
@@ -4858,7 +4898,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4868,14 +4908,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506703</v>
+        <v>506352</v>
       </c>
       <c r="R34" t="n">
-        <v>7053305</v>
+        <v>7053112</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4936,12 +4976,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4959,10 +4999,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597978</v>
+        <v>121601171</v>
       </c>
       <c r="B35" t="n">
-        <v>79719</v>
+        <v>90720</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4971,43 +5011,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506470</v>
+        <v>506381</v>
       </c>
       <c r="R35" t="n">
-        <v>7053032</v>
+        <v>7053357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5058,22 +5098,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5091,10 +5131,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597096</v>
+        <v>121598801</v>
       </c>
       <c r="B36" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5107,39 +5147,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506735</v>
+        <v>506390</v>
       </c>
       <c r="R36" t="n">
-        <v>7053336</v>
+        <v>7053088</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5200,12 +5240,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5223,10 +5263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597523</v>
+        <v>121601508</v>
       </c>
       <c r="B37" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5239,39 +5279,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506599</v>
+        <v>506490</v>
       </c>
       <c r="R37" t="n">
-        <v>7053253</v>
+        <v>7053371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5332,12 +5367,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5355,10 +5390,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601916</v>
+        <v>121597044</v>
       </c>
       <c r="B38" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5367,25 +5402,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5395,10 +5430,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506663</v>
+        <v>506743</v>
       </c>
       <c r="R38" t="n">
-        <v>7053393</v>
+        <v>7053366</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5433,11 +5468,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5446,31 +5476,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5487,10 +5492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601859</v>
+        <v>121597940</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5503,21 +5508,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5527,10 +5532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506600</v>
+        <v>506473</v>
       </c>
       <c r="R39" t="n">
-        <v>7053390</v>
+        <v>7053034</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5581,22 +5586,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5614,10 +5619,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598608</v>
+        <v>121597408</v>
       </c>
       <c r="B40" t="n">
-        <v>97059</v>
+        <v>91403</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5630,44 +5635,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506426</v>
+        <v>506592</v>
       </c>
       <c r="R40" t="n">
-        <v>7053063</v>
+        <v>7053288</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5702,11 +5702,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5719,6 +5714,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5736,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598834</v>
+        <v>121598953</v>
       </c>
       <c r="B41" t="n">
-        <v>57509</v>
+        <v>90720</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5752,53 +5767,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506403</v>
+        <v>506336</v>
       </c>
       <c r="R41" t="n">
-        <v>7053127</v>
+        <v>7053124</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5845,6 +5846,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5862,10 +5883,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121602116</v>
+        <v>121597096</v>
       </c>
       <c r="B42" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5878,21 +5899,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5907,10 +5928,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506843</v>
+        <v>506735</v>
       </c>
       <c r="R42" t="n">
-        <v>7053491</v>
+        <v>7053336</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5994,10 +6015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121597408</v>
+        <v>121598719</v>
       </c>
       <c r="B43" t="n">
-        <v>91403</v>
+        <v>57372</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6006,43 +6027,48 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506592</v>
+        <v>506374</v>
       </c>
       <c r="R43" t="n">
-        <v>7053288</v>
+        <v>7053093</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6103,12 +6129,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6126,10 +6152,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598719</v>
+        <v>121601957</v>
       </c>
       <c r="B44" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6142,44 +6168,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506374</v>
+        <v>506684</v>
       </c>
       <c r="R44" t="n">
-        <v>7053093</v>
+        <v>7053378</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6240,12 +6261,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6263,10 +6284,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121597990</v>
+        <v>121601347</v>
       </c>
       <c r="B45" t="n">
-        <v>79725</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6275,20 +6296,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6297,21 +6318,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506470</v>
+        <v>506473</v>
       </c>
       <c r="R45" t="n">
-        <v>7053032</v>
+        <v>7053383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6362,22 +6378,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6395,10 +6411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121597382</v>
+        <v>121601859</v>
       </c>
       <c r="B46" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6411,29 +6427,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
@@ -6443,7 +6454,7 @@
         <v>506600</v>
       </c>
       <c r="R46" t="n">
-        <v>7053289</v>
+        <v>7053390</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6504,12 +6515,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6527,10 +6538,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121599143</v>
+        <v>121601357</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6543,37 +6554,51 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506325</v>
+        <v>506460</v>
       </c>
       <c r="R47" t="n">
-        <v>7053209</v>
+        <v>7053365</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6617,26 +6642,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6654,10 +6659,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121601665</v>
+        <v>121598549</v>
       </c>
       <c r="B48" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6670,37 +6675,51 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506512</v>
+        <v>506432</v>
       </c>
       <c r="R48" t="n">
-        <v>7053384</v>
+        <v>7053087</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6744,26 +6763,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6781,10 +6780,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121597797</v>
+        <v>121597382</v>
       </c>
       <c r="B49" t="n">
-        <v>91403</v>
+        <v>90716</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6793,25 +6792,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6826,10 +6825,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506488</v>
+        <v>506600</v>
       </c>
       <c r="R49" t="n">
-        <v>7053023</v>
+        <v>7053289</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6890,12 +6889,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6913,10 +6912,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121597320</v>
+        <v>121596964</v>
       </c>
       <c r="B50" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6929,44 +6928,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506606</v>
+        <v>506818</v>
       </c>
       <c r="R50" t="n">
-        <v>7053294</v>
+        <v>7053423</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7001,11 +6990,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -7032,12 +7016,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7055,10 +7039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121596964</v>
+        <v>121598834</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7071,34 +7055,53 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506818</v>
+        <v>506403</v>
       </c>
       <c r="R51" t="n">
-        <v>7053423</v>
+        <v>7053127</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7145,26 +7148,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7182,10 +7165,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598801</v>
+        <v>121597247</v>
       </c>
       <c r="B52" t="n">
-        <v>57372</v>
+        <v>90716</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7198,39 +7181,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506390</v>
+        <v>506669</v>
       </c>
       <c r="R52" t="n">
-        <v>7053088</v>
+        <v>7053308</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7291,12 +7274,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7314,10 +7297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121598549</v>
+        <v>121599490</v>
       </c>
       <c r="B53" t="n">
-        <v>57509</v>
+        <v>79690</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7330,51 +7313,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506432</v>
+        <v>506379</v>
       </c>
       <c r="R53" t="n">
-        <v>7053087</v>
+        <v>7053186</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7418,6 +7392,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7435,10 +7429,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121601357</v>
+        <v>121596987</v>
       </c>
       <c r="B54" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7451,51 +7445,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506460</v>
+        <v>506796</v>
       </c>
       <c r="R54" t="n">
-        <v>7053365</v>
+        <v>7053411</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7539,6 +7519,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -4334,10 +4334,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597690</v>
+        <v>121599680</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>79719</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4346,48 +4346,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506558</v>
+        <v>506380</v>
       </c>
       <c r="R30" t="n">
-        <v>7053116</v>
+        <v>7053232</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4438,22 +4433,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4471,10 +4466,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121599680</v>
+        <v>121597690</v>
       </c>
       <c r="B31" t="n">
-        <v>79719</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4483,43 +4478,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506380</v>
+        <v>506558</v>
       </c>
       <c r="R31" t="n">
-        <v>7053232</v>
+        <v>7053116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4570,22 +4570,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121601508</v>
+        <v>121597940</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5279,21 +5279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506490</v>
+        <v>506473</v>
       </c>
       <c r="R37" t="n">
-        <v>7053371</v>
+        <v>7053034</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121597940</v>
+        <v>121601508</v>
       </c>
       <c r="B39" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506473</v>
+        <v>506490</v>
       </c>
       <c r="R39" t="n">
-        <v>7053034</v>
+        <v>7053371</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5586,22 +5586,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5619,10 +5619,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597408</v>
+        <v>121598953</v>
       </c>
       <c r="B40" t="n">
-        <v>91403</v>
+        <v>90720</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5660,14 +5660,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506592</v>
+        <v>506336</v>
       </c>
       <c r="R40" t="n">
-        <v>7053288</v>
+        <v>7053124</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5728,12 +5728,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598953</v>
+        <v>121597408</v>
       </c>
       <c r="B41" t="n">
-        <v>90720</v>
+        <v>91403</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5763,25 +5763,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5792,14 +5792,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506336</v>
+        <v>506592</v>
       </c>
       <c r="R41" t="n">
-        <v>7053124</v>
+        <v>7053288</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121601347</v>
+        <v>121601357</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6300,37 +6300,51 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506473</v>
+        <v>506460</v>
       </c>
       <c r="R45" t="n">
-        <v>7053383</v>
+        <v>7053365</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6374,26 +6388,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6411,7 +6405,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601859</v>
+        <v>121601347</v>
       </c>
       <c r="B46" t="n">
         <v>78609</v>
@@ -6447,14 +6441,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506600</v>
+        <v>506473</v>
       </c>
       <c r="R46" t="n">
-        <v>7053390</v>
+        <v>7053383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6538,10 +6532,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601357</v>
+        <v>121601859</v>
       </c>
       <c r="B47" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6554,51 +6548,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506460</v>
+        <v>506600</v>
       </c>
       <c r="R47" t="n">
-        <v>7053365</v>
+        <v>7053390</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6642,6 +6622,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7039,10 +7039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121598834</v>
+        <v>121601888</v>
       </c>
       <c r="B51" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7055,53 +7055,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506403</v>
+        <v>506625</v>
       </c>
       <c r="R51" t="n">
-        <v>7053127</v>
+        <v>7053387</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7148,6 +7129,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7165,10 +7166,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121597247</v>
+        <v>121599490</v>
       </c>
       <c r="B52" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7181,39 +7182,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506669</v>
+        <v>506379</v>
       </c>
       <c r="R52" t="n">
-        <v>7053308</v>
+        <v>7053186</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7264,22 +7265,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7297,10 +7298,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121599490</v>
+        <v>121596987</v>
       </c>
       <c r="B53" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7313,42 +7314,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506379</v>
+        <v>506796</v>
       </c>
       <c r="R53" t="n">
-        <v>7053186</v>
+        <v>7053411</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7396,22 +7392,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7429,10 +7425,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121596987</v>
+        <v>121597247</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7445,37 +7441,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506796</v>
+        <v>506669</v>
       </c>
       <c r="R54" t="n">
-        <v>7053411</v>
+        <v>7053308</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7533,12 +7534,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7556,10 +7557,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121601888</v>
+        <v>121598834</v>
       </c>
       <c r="B55" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7572,34 +7573,53 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506625</v>
+        <v>506403</v>
       </c>
       <c r="R55" t="n">
-        <v>7053387</v>
+        <v>7053127</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7646,26 +7666,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -4334,10 +4334,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121599680</v>
+        <v>121597690</v>
       </c>
       <c r="B30" t="n">
-        <v>79719</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4346,43 +4346,48 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506380</v>
+        <v>506558</v>
       </c>
       <c r="R30" t="n">
-        <v>7053232</v>
+        <v>7053116</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4433,22 +4438,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4466,10 +4471,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597690</v>
+        <v>121599680</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>79719</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4478,48 +4483,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506558</v>
+        <v>506380</v>
       </c>
       <c r="R31" t="n">
-        <v>7053116</v>
+        <v>7053232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4570,22 +4570,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5619,10 +5619,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598953</v>
+        <v>121597408</v>
       </c>
       <c r="B40" t="n">
-        <v>90720</v>
+        <v>91403</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5660,14 +5660,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506336</v>
+        <v>506592</v>
       </c>
       <c r="R40" t="n">
-        <v>7053124</v>
+        <v>7053288</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5728,12 +5728,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121597408</v>
+        <v>121598953</v>
       </c>
       <c r="B41" t="n">
-        <v>91403</v>
+        <v>90720</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5763,25 +5763,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5792,14 +5792,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506592</v>
+        <v>506336</v>
       </c>
       <c r="R41" t="n">
-        <v>7053288</v>
+        <v>7053124</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -7039,10 +7039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121601888</v>
+        <v>121598834</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7055,34 +7055,53 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506625</v>
+        <v>506403</v>
       </c>
       <c r="R51" t="n">
-        <v>7053387</v>
+        <v>7053127</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7129,26 +7148,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7166,10 +7165,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121599490</v>
+        <v>121597247</v>
       </c>
       <c r="B52" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7182,39 +7181,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506379</v>
+        <v>506669</v>
       </c>
       <c r="R52" t="n">
-        <v>7053186</v>
+        <v>7053308</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7265,22 +7264,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7298,10 +7297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121596987</v>
+        <v>121599490</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7314,37 +7313,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506796</v>
+        <v>506379</v>
       </c>
       <c r="R53" t="n">
-        <v>7053411</v>
+        <v>7053186</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7392,22 +7396,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7425,10 +7429,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121597247</v>
+        <v>121596987</v>
       </c>
       <c r="B54" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7441,42 +7445,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506669</v>
+        <v>506796</v>
       </c>
       <c r="R54" t="n">
-        <v>7053308</v>
+        <v>7053411</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7534,12 +7533,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7557,10 +7556,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121598834</v>
+        <v>121601888</v>
       </c>
       <c r="B55" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7573,53 +7572,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506403</v>
+        <v>506625</v>
       </c>
       <c r="R55" t="n">
-        <v>7053127</v>
+        <v>7053387</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7666,6 +7646,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597523</v>
+        <v>121601665</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,39 +2082,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506599</v>
+        <v>506512</v>
       </c>
       <c r="R13" t="n">
-        <v>7053253</v>
+        <v>7053384</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2175,12 +2170,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2198,10 +2193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121598608</v>
+        <v>121597408</v>
       </c>
       <c r="B14" t="n">
-        <v>97059</v>
+        <v>91411</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2214,44 +2209,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506426</v>
+        <v>506592</v>
       </c>
       <c r="R14" t="n">
-        <v>7053063</v>
+        <v>7053288</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2286,11 +2276,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2303,6 +2288,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597673</v>
+        <v>121601872</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2356,12 +2361,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506553</v>
+        <v>506612</v>
       </c>
       <c r="R15" t="n">
-        <v>7053113</v>
+        <v>7053395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597130</v>
+        <v>121597247</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>90724</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,32 +2473,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2507,10 +2502,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506703</v>
+        <v>506669</v>
       </c>
       <c r="R16" t="n">
-        <v>7053305</v>
+        <v>7053308</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,12 +2566,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2594,10 +2589,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121599094</v>
+        <v>121597690</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2610,39 +2605,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506328</v>
+        <v>506558</v>
       </c>
       <c r="R17" t="n">
-        <v>7053195</v>
+        <v>7053116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2693,22 +2693,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597990</v>
+        <v>121598719</v>
       </c>
       <c r="B18" t="n">
-        <v>79725</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2738,43 +2738,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506470</v>
+        <v>506374</v>
       </c>
       <c r="R18" t="n">
-        <v>7053032</v>
+        <v>7053093</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,22 +2830,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2858,10 +2863,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597306</v>
+        <v>121601916</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2874,44 +2879,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506628</v>
+        <v>506663</v>
       </c>
       <c r="R19" t="n">
-        <v>7053277</v>
+        <v>7053393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2948,7 +2943,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>På flertalet granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,12 +2972,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3000,10 +2995,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121598813</v>
+        <v>121601859</v>
       </c>
       <c r="B20" t="n">
-        <v>90716</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3016,48 +3011,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506403</v>
+        <v>506600</v>
       </c>
       <c r="R20" t="n">
-        <v>7053116</v>
+        <v>7053390</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3118,12 +3099,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3141,10 +3122,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597978</v>
+        <v>121601957</v>
       </c>
       <c r="B21" t="n">
-        <v>79719</v>
+        <v>90728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3153,31 +3134,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3186,10 +3167,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506470</v>
+        <v>506684</v>
       </c>
       <c r="R21" t="n">
-        <v>7053032</v>
+        <v>7053378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3240,22 +3221,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3273,10 +3254,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597320</v>
+        <v>121601347</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3289,44 +3270,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506606</v>
+        <v>506473</v>
       </c>
       <c r="R22" t="n">
-        <v>7053294</v>
+        <v>7053383</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3361,11 +3332,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,12 +3358,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3415,10 +3381,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601665</v>
+        <v>121597797</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>91411</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3427,38 +3393,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506512</v>
+        <v>506488</v>
       </c>
       <c r="R23" t="n">
-        <v>7053384</v>
+        <v>7053023</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3519,12 +3490,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3542,10 +3513,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121602039</v>
+        <v>121596987</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3582,13 +3553,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506765</v>
+        <v>506796</v>
       </c>
       <c r="R24" t="n">
-        <v>7053438</v>
+        <v>7053411</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3669,10 +3640,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598985</v>
+        <v>121597990</v>
       </c>
       <c r="B25" t="n">
-        <v>57372</v>
+        <v>79732</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3681,48 +3652,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506335</v>
+        <v>506470</v>
       </c>
       <c r="R25" t="n">
-        <v>7053140</v>
+        <v>7053032</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3773,22 +3739,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3806,10 +3772,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121602116</v>
+        <v>121602039</v>
       </c>
       <c r="B26" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3822,39 +3788,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506843</v>
+        <v>506765</v>
       </c>
       <c r="R26" t="n">
-        <v>7053491</v>
+        <v>7053438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3915,12 +3876,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3938,10 +3899,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121598773</v>
+        <v>121598813</v>
       </c>
       <c r="B27" t="n">
-        <v>90720</v>
+        <v>90724</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3954,24 +3915,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3983,10 +3953,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506378</v>
+        <v>506403</v>
       </c>
       <c r="R27" t="n">
-        <v>7053113</v>
+        <v>7053116</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4047,12 +4017,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4070,10 +4040,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601872</v>
+        <v>121598953</v>
       </c>
       <c r="B28" t="n">
-        <v>57372</v>
+        <v>90728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4086,39 +4056,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506612</v>
+        <v>506336</v>
       </c>
       <c r="R28" t="n">
-        <v>7053395</v>
+        <v>7053124</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4179,12 +4149,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4202,10 +4172,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121601916</v>
+        <v>121597130</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4218,34 +4188,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506663</v>
+        <v>506703</v>
       </c>
       <c r="R29" t="n">
-        <v>7053393</v>
+        <v>7053305</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4280,11 +4260,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4311,12 +4286,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4334,10 +4309,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597690</v>
+        <v>121599143</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4350,44 +4325,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506558</v>
+        <v>506325</v>
       </c>
       <c r="R30" t="n">
-        <v>7053116</v>
+        <v>7053209</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4448,12 +4413,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4471,10 +4436,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121599680</v>
+        <v>121598902</v>
       </c>
       <c r="B31" t="n">
-        <v>79719</v>
+        <v>57373</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4483,43 +4448,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506380</v>
+        <v>506352</v>
       </c>
       <c r="R31" t="n">
-        <v>7053232</v>
+        <v>7053112</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4570,22 +4540,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4603,10 +4573,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597797</v>
+        <v>121598834</v>
       </c>
       <c r="B32" t="n">
-        <v>91403</v>
+        <v>57510</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4615,43 +4585,57 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506488</v>
+        <v>506403</v>
       </c>
       <c r="R32" t="n">
-        <v>7053023</v>
+        <v>7053127</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4698,26 +4682,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4735,10 +4699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121599143</v>
+        <v>121598608</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>97067</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4747,38 +4711,48 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506325</v>
+        <v>506426</v>
       </c>
       <c r="R33" t="n">
-        <v>7053209</v>
+        <v>7053063</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4813,6 +4787,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4825,26 +4804,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4862,10 +4821,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121598902</v>
+        <v>121597978</v>
       </c>
       <c r="B34" t="n">
-        <v>57372</v>
+        <v>79726</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4874,48 +4833,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506352</v>
+        <v>506470</v>
       </c>
       <c r="R34" t="n">
-        <v>7053112</v>
+        <v>7053032</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4966,22 +4920,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4999,10 +4953,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121601171</v>
+        <v>121597523</v>
       </c>
       <c r="B35" t="n">
-        <v>90720</v>
+        <v>90746</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5015,21 +4969,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5040,14 +4994,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506381</v>
+        <v>506599</v>
       </c>
       <c r="R35" t="n">
-        <v>7053357</v>
+        <v>7053253</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5131,10 +5085,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121598801</v>
+        <v>121599490</v>
       </c>
       <c r="B36" t="n">
-        <v>57372</v>
+        <v>79697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5147,39 +5101,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506390</v>
+        <v>506379</v>
       </c>
       <c r="R36" t="n">
-        <v>7053088</v>
+        <v>7053186</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5230,22 +5184,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5263,10 +5217,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597940</v>
+        <v>121601357</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>57510</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5279,37 +5233,51 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506473</v>
+        <v>506460</v>
       </c>
       <c r="R37" t="n">
-        <v>7053034</v>
+        <v>7053365</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5353,26 +5321,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5390,10 +5338,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597044</v>
+        <v>121602116</v>
       </c>
       <c r="B38" t="n">
-        <v>97059</v>
+        <v>90728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5402,38 +5350,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506743</v>
+        <v>506843</v>
       </c>
       <c r="R38" t="n">
-        <v>7053366</v>
+        <v>7053491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5476,6 +5429,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5492,10 +5470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601508</v>
+        <v>121596964</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5532,10 +5510,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506490</v>
+        <v>506818</v>
       </c>
       <c r="R39" t="n">
-        <v>7053371</v>
+        <v>7053423</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5619,10 +5597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597408</v>
+        <v>121598985</v>
       </c>
       <c r="B40" t="n">
-        <v>91403</v>
+        <v>57373</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5631,43 +5609,48 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506592</v>
+        <v>506335</v>
       </c>
       <c r="R40" t="n">
-        <v>7053288</v>
+        <v>7053140</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5728,12 +5711,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5751,10 +5734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598953</v>
+        <v>121601508</v>
       </c>
       <c r="B41" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5767,39 +5750,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506336</v>
+        <v>506490</v>
       </c>
       <c r="R41" t="n">
-        <v>7053124</v>
+        <v>7053371</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5860,12 +5838,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5883,10 +5861,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121597096</v>
+        <v>121599094</v>
       </c>
       <c r="B42" t="n">
-        <v>90738</v>
+        <v>79697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5899,39 +5877,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506735</v>
+        <v>506328</v>
       </c>
       <c r="R42" t="n">
-        <v>7053336</v>
+        <v>7053195</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5982,22 +5960,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6015,10 +5993,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121598719</v>
+        <v>121597940</v>
       </c>
       <c r="B43" t="n">
-        <v>57372</v>
+        <v>79697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6031,44 +6009,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506374</v>
+        <v>506473</v>
       </c>
       <c r="R43" t="n">
-        <v>7053093</v>
+        <v>7053034</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6119,22 +6087,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6152,10 +6120,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121601957</v>
+        <v>121598549</v>
       </c>
       <c r="B44" t="n">
-        <v>90720</v>
+        <v>57510</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6168,42 +6136,51 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506684</v>
+        <v>506432</v>
       </c>
       <c r="R44" t="n">
-        <v>7053378</v>
+        <v>7053087</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6247,26 +6224,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6284,10 +6241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121601357</v>
+        <v>121597673</v>
       </c>
       <c r="B45" t="n">
-        <v>57509</v>
+        <v>57373</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6300,31 +6257,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6338,13 +6291,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506460</v>
+        <v>506553</v>
       </c>
       <c r="R45" t="n">
-        <v>7053365</v>
+        <v>7053113</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6388,6 +6341,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6405,10 +6378,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601347</v>
+        <v>121601888</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6441,14 +6414,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506473</v>
+        <v>506625</v>
       </c>
       <c r="R46" t="n">
-        <v>7053383</v>
+        <v>7053387</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6532,10 +6505,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601859</v>
+        <v>121597044</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>97067</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6544,25 +6517,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6572,10 +6545,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506600</v>
+        <v>506743</v>
       </c>
       <c r="R47" t="n">
-        <v>7053390</v>
+        <v>7053366</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6618,31 +6591,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6659,10 +6607,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121598549</v>
+        <v>121597096</v>
       </c>
       <c r="B48" t="n">
-        <v>57509</v>
+        <v>90746</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6675,51 +6623,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506432</v>
+        <v>506735</v>
       </c>
       <c r="R48" t="n">
-        <v>7053087</v>
+        <v>7053336</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6763,6 +6702,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6780,10 +6739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121597382</v>
+        <v>121597320</v>
       </c>
       <c r="B49" t="n">
-        <v>90716</v>
+        <v>57357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6796,39 +6755,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506600</v>
+        <v>506606</v>
       </c>
       <c r="R49" t="n">
-        <v>7053289</v>
+        <v>7053294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6861,6 +6825,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6912,10 +6881,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121596964</v>
+        <v>121598773</v>
       </c>
       <c r="B50" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6928,34 +6897,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506818</v>
+        <v>506378</v>
       </c>
       <c r="R50" t="n">
-        <v>7053423</v>
+        <v>7053113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7016,12 +6990,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7039,10 +7013,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121598834</v>
+        <v>121598801</v>
       </c>
       <c r="B51" t="n">
-        <v>57509</v>
+        <v>57373</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7055,41 +7029,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7098,10 +7058,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506403</v>
+        <v>506390</v>
       </c>
       <c r="R51" t="n">
-        <v>7053127</v>
+        <v>7053088</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7148,6 +7108,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7165,10 +7145,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121597247</v>
+        <v>121601171</v>
       </c>
       <c r="B52" t="n">
-        <v>90716</v>
+        <v>90728</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7181,21 +7161,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7206,14 +7186,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506669</v>
+        <v>506381</v>
       </c>
       <c r="R52" t="n">
-        <v>7053308</v>
+        <v>7053357</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7274,12 +7254,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7297,10 +7277,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121599490</v>
+        <v>121597382</v>
       </c>
       <c r="B53" t="n">
-        <v>79690</v>
+        <v>90724</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7313,39 +7293,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506379</v>
+        <v>506600</v>
       </c>
       <c r="R53" t="n">
-        <v>7053186</v>
+        <v>7053289</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7396,22 +7376,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7429,10 +7409,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121596987</v>
+        <v>121599680</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7441,41 +7421,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506796</v>
+        <v>506380</v>
       </c>
       <c r="R54" t="n">
-        <v>7053411</v>
+        <v>7053232</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7523,22 +7508,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7556,10 +7541,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121601888</v>
+        <v>121597306</v>
       </c>
       <c r="B55" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7572,34 +7557,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506625</v>
+        <v>506628</v>
       </c>
       <c r="R55" t="n">
-        <v>7053387</v>
+        <v>7053277</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7634,6 +7629,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7686,7 +7686,7 @@
         <v>121597218</v>
       </c>
       <c r="B56" t="n">
-        <v>55958</v>
+        <v>55959</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>121597364</v>
       </c>
       <c r="B57" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2325,10 +2325,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121601872</v>
+        <v>121597247</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2341,39 +2341,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506612</v>
+        <v>506669</v>
       </c>
       <c r="R15" t="n">
-        <v>7053395</v>
+        <v>7053308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597247</v>
+        <v>121597690</v>
       </c>
       <c r="B16" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,39 +2473,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506669</v>
+        <v>506558</v>
       </c>
       <c r="R16" t="n">
-        <v>7053308</v>
+        <v>7053116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2566,12 +2571,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2589,7 +2594,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597690</v>
+        <v>121598719</v>
       </c>
       <c r="B17" t="n">
         <v>57373</v>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506558</v>
+        <v>506374</v>
       </c>
       <c r="R17" t="n">
-        <v>7053116</v>
+        <v>7053093</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2703,12 +2708,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2726,7 +2731,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121598719</v>
+        <v>121601872</v>
       </c>
       <c r="B18" t="n">
         <v>57373</v>
@@ -2765,21 +2770,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506374</v>
+        <v>506612</v>
       </c>
       <c r="R18" t="n">
-        <v>7053093</v>
+        <v>7053395</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121602116</v>
+        <v>121596964</v>
       </c>
       <c r="B38" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5354,39 +5354,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506843</v>
+        <v>506818</v>
       </c>
       <c r="R38" t="n">
-        <v>7053491</v>
+        <v>7053423</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5447,12 +5442,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5470,10 +5465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121596964</v>
+        <v>121602116</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5486,34 +5481,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506818</v>
+        <v>506843</v>
       </c>
       <c r="R39" t="n">
-        <v>7053423</v>
+        <v>7053491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598985</v>
+        <v>121601508</v>
       </c>
       <c r="B40" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5613,44 +5613,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506335</v>
+        <v>506490</v>
       </c>
       <c r="R40" t="n">
-        <v>7053140</v>
+        <v>7053371</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5711,12 +5701,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5734,10 +5724,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121601508</v>
+        <v>121598985</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5750,34 +5740,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506490</v>
+        <v>506335</v>
       </c>
       <c r="R41" t="n">
-        <v>7053371</v>
+        <v>7053140</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601888</v>
+        <v>121597044</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6390,25 +6390,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6418,10 +6418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506625</v>
+        <v>506743</v>
       </c>
       <c r="R46" t="n">
-        <v>7053387</v>
+        <v>7053366</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6464,31 +6464,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6505,10 +6480,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121597044</v>
+        <v>121601888</v>
       </c>
       <c r="B47" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6517,25 +6492,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6545,10 +6520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506743</v>
+        <v>506625</v>
       </c>
       <c r="R47" t="n">
-        <v>7053366</v>
+        <v>7053387</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6591,6 +6566,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -4953,10 +4953,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597523</v>
+        <v>121601357</v>
       </c>
       <c r="B35" t="n">
-        <v>90746</v>
+        <v>57510</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4969,42 +4969,51 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506599</v>
+        <v>506460</v>
       </c>
       <c r="R35" t="n">
-        <v>7053253</v>
+        <v>7053365</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5048,26 +5057,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5085,10 +5074,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121599490</v>
+        <v>121597523</v>
       </c>
       <c r="B36" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5101,39 +5090,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506379</v>
+        <v>506599</v>
       </c>
       <c r="R36" t="n">
-        <v>7053186</v>
+        <v>7053253</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5184,22 +5173,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5217,10 +5206,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121601357</v>
+        <v>121599490</v>
       </c>
       <c r="B37" t="n">
-        <v>57510</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5233,51 +5222,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506460</v>
+        <v>506379</v>
       </c>
       <c r="R37" t="n">
-        <v>7053365</v>
+        <v>7053186</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5321,6 +5301,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121596964</v>
+        <v>121602116</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5354,34 +5354,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506818</v>
+        <v>506843</v>
       </c>
       <c r="R38" t="n">
-        <v>7053423</v>
+        <v>7053491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5442,12 +5447,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5465,10 +5470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121602116</v>
+        <v>121596964</v>
       </c>
       <c r="B39" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5481,39 +5486,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506843</v>
+        <v>506818</v>
       </c>
       <c r="R39" t="n">
-        <v>7053491</v>
+        <v>7053423</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121601508</v>
+        <v>121598985</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5613,34 +5613,44 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506490</v>
+        <v>506335</v>
       </c>
       <c r="R40" t="n">
-        <v>7053371</v>
+        <v>7053140</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5701,12 +5711,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5724,10 +5734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598985</v>
+        <v>121601508</v>
       </c>
       <c r="B41" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5740,44 +5750,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506335</v>
+        <v>506490</v>
       </c>
       <c r="R41" t="n">
-        <v>7053140</v>
+        <v>7053371</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597096</v>
+        <v>121601665</v>
       </c>
       <c r="B13" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,39 +2082,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506735</v>
+        <v>506512</v>
       </c>
       <c r="R13" t="n">
-        <v>7053336</v>
+        <v>7053384</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2175,12 +2170,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2198,10 +2193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121602039</v>
+        <v>121598608</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2210,38 +2205,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506765</v>
+        <v>506426</v>
       </c>
       <c r="R14" t="n">
-        <v>7053438</v>
+        <v>7053063</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,6 +2281,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2288,26 +2298,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2325,10 +2315,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121601888</v>
+        <v>121601171</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2341,34 +2331,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506625</v>
+        <v>506381</v>
       </c>
       <c r="R15" t="n">
-        <v>7053387</v>
+        <v>7053357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,12 +2424,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2452,10 +2447,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597990</v>
+        <v>121599680</v>
       </c>
       <c r="B16" t="n">
-        <v>79732</v>
+        <v>79726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2468,39 +2463,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506470</v>
+        <v>506380</v>
       </c>
       <c r="R16" t="n">
-        <v>7053032</v>
+        <v>7053232</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2584,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121601957</v>
+        <v>121597382</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2600,21 +2595,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2629,10 +2624,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506684</v>
+        <v>506600</v>
       </c>
       <c r="R17" t="n">
-        <v>7053378</v>
+        <v>7053289</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2693,12 +2688,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2716,10 +2711,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121601665</v>
+        <v>121598985</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2732,34 +2727,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506512</v>
+        <v>506335</v>
       </c>
       <c r="R18" t="n">
-        <v>7053384</v>
+        <v>7053140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2820,12 +2825,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2843,10 +2848,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596964</v>
+        <v>121601357</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2859,37 +2864,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506818</v>
+        <v>506460</v>
       </c>
       <c r="R19" t="n">
-        <v>7053423</v>
+        <v>7053365</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2933,26 +2952,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2970,10 +2969,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121598813</v>
+        <v>121597990</v>
       </c>
       <c r="B20" t="n">
-        <v>90724</v>
+        <v>79732</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2982,52 +2981,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506403</v>
+        <v>506470</v>
       </c>
       <c r="R20" t="n">
-        <v>7053116</v>
+        <v>7053032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,22 +3068,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3111,7 +3101,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121598719</v>
+        <v>121598902</v>
       </c>
       <c r="B21" t="n">
         <v>57373</v>
@@ -3161,10 +3151,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506374</v>
+        <v>506352</v>
       </c>
       <c r="R21" t="n">
-        <v>7053093</v>
+        <v>7053112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3248,10 +3238,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598801</v>
+        <v>121602039</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3264,39 +3254,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506390</v>
+        <v>506765</v>
       </c>
       <c r="R22" t="n">
-        <v>7053088</v>
+        <v>7053438</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3357,12 +3342,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3380,10 +3365,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597320</v>
+        <v>121597408</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>91411</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3392,48 +3377,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506606</v>
+        <v>506592</v>
       </c>
       <c r="R23" t="n">
-        <v>7053294</v>
+        <v>7053288</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3466,11 +3446,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3522,10 +3497,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121598953</v>
+        <v>121597940</v>
       </c>
       <c r="B24" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3538,39 +3513,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506336</v>
+        <v>506473</v>
       </c>
       <c r="R24" t="n">
-        <v>7053124</v>
+        <v>7053034</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3621,22 +3591,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3654,10 +3624,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598902</v>
+        <v>121599094</v>
       </c>
       <c r="B25" t="n">
-        <v>57373</v>
+        <v>79697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3670,44 +3640,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506352</v>
+        <v>506328</v>
       </c>
       <c r="R25" t="n">
-        <v>7053112</v>
+        <v>7053195</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3758,22 +3723,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3791,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601872</v>
+        <v>121599143</v>
       </c>
       <c r="B26" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3807,39 +3772,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506612</v>
+        <v>506325</v>
       </c>
       <c r="R26" t="n">
-        <v>7053395</v>
+        <v>7053209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3900,12 +3860,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3923,10 +3883,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121599143</v>
+        <v>121597978</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3935,38 +3895,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506325</v>
+        <v>506470</v>
       </c>
       <c r="R27" t="n">
-        <v>7053209</v>
+        <v>7053032</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4017,22 +3982,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4050,10 +4015,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121598549</v>
+        <v>121601508</v>
       </c>
       <c r="B28" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4066,51 +4031,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506432</v>
+        <v>506490</v>
       </c>
       <c r="R28" t="n">
-        <v>7053087</v>
+        <v>7053371</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4154,6 +4105,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4171,7 +4142,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121598773</v>
+        <v>121602116</v>
       </c>
       <c r="B29" t="n">
         <v>90728</v>
@@ -4212,14 +4183,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506378</v>
+        <v>506843</v>
       </c>
       <c r="R29" t="n">
-        <v>7053113</v>
+        <v>7053491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4303,10 +4274,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601357</v>
+        <v>121598719</v>
       </c>
       <c r="B30" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4319,31 +4290,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4357,13 +4324,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506460</v>
+        <v>506374</v>
       </c>
       <c r="R30" t="n">
-        <v>7053365</v>
+        <v>7053093</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4407,6 +4374,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4424,10 +4411,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597130</v>
+        <v>121596964</v>
       </c>
       <c r="B31" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4440,44 +4427,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506703</v>
+        <v>506818</v>
       </c>
       <c r="R31" t="n">
-        <v>7053305</v>
+        <v>7053423</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4538,12 +4515,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4561,10 +4538,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121601347</v>
+        <v>121597690</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4577,34 +4554,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506473</v>
+        <v>506558</v>
       </c>
       <c r="R32" t="n">
-        <v>7053383</v>
+        <v>7053116</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4665,12 +4652,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4825,10 +4812,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597044</v>
+        <v>121597306</v>
       </c>
       <c r="B34" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4837,38 +4824,48 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506743</v>
+        <v>506628</v>
       </c>
       <c r="R34" t="n">
-        <v>7053366</v>
+        <v>7053277</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4903,6 +4900,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4911,6 +4913,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4927,10 +4954,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597978</v>
+        <v>121597797</v>
       </c>
       <c r="B35" t="n">
-        <v>79726</v>
+        <v>91411</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4943,27 +4970,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4972,10 +4999,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506470</v>
+        <v>506488</v>
       </c>
       <c r="R35" t="n">
-        <v>7053032</v>
+        <v>7053023</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5026,22 +5053,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5059,10 +5086,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597306</v>
+        <v>121598773</v>
       </c>
       <c r="B36" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5075,44 +5102,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506628</v>
+        <v>506378</v>
       </c>
       <c r="R36" t="n">
-        <v>7053277</v>
+        <v>7053113</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5147,11 +5169,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5178,12 +5195,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5201,10 +5218,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121599094</v>
+        <v>121601957</v>
       </c>
       <c r="B37" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5217,39 +5234,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506328</v>
+        <v>506684</v>
       </c>
       <c r="R37" t="n">
-        <v>7053195</v>
+        <v>7053378</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5300,22 +5317,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5333,10 +5350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597382</v>
+        <v>121601888</v>
       </c>
       <c r="B38" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5349,39 +5366,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506600</v>
+        <v>506625</v>
       </c>
       <c r="R38" t="n">
-        <v>7053289</v>
+        <v>7053387</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5442,12 +5454,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5465,10 +5477,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121598985</v>
+        <v>121601859</v>
       </c>
       <c r="B39" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5481,44 +5493,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506335</v>
+        <v>506600</v>
       </c>
       <c r="R39" t="n">
-        <v>7053140</v>
+        <v>7053390</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5579,12 +5581,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5602,10 +5604,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597408</v>
+        <v>121597247</v>
       </c>
       <c r="B40" t="n">
-        <v>91411</v>
+        <v>90724</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5614,25 +5616,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5647,10 +5649,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506592</v>
+        <v>506669</v>
       </c>
       <c r="R40" t="n">
-        <v>7053288</v>
+        <v>7053308</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5711,12 +5713,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5734,10 +5736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121602116</v>
+        <v>121598813</v>
       </c>
       <c r="B41" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5750,24 +5752,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -5775,14 +5786,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506843</v>
+        <v>506403</v>
       </c>
       <c r="R41" t="n">
-        <v>7053491</v>
+        <v>7053116</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5843,12 +5854,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5866,10 +5877,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121601916</v>
+        <v>121597130</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5882,34 +5893,44 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506663</v>
+        <v>506703</v>
       </c>
       <c r="R42" t="n">
-        <v>7053393</v>
+        <v>7053305</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5944,11 +5965,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5975,12 +5991,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5998,10 +6014,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121601171</v>
+        <v>121601347</v>
       </c>
       <c r="B43" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6014,39 +6030,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506381</v>
+        <v>506473</v>
       </c>
       <c r="R43" t="n">
-        <v>7053357</v>
+        <v>7053383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6107,12 +6118,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6130,7 +6141,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121601859</v>
+        <v>121601916</v>
       </c>
       <c r="B44" t="n">
         <v>78616</v>
@@ -6170,10 +6181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506600</v>
+        <v>506663</v>
       </c>
       <c r="R44" t="n">
-        <v>7053390</v>
+        <v>7053393</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6206,6 +6217,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6257,7 +6273,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121597523</v>
+        <v>121597096</v>
       </c>
       <c r="B45" t="n">
         <v>90746</v>
@@ -6302,10 +6318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506599</v>
+        <v>506735</v>
       </c>
       <c r="R45" t="n">
-        <v>7053253</v>
+        <v>7053336</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6389,10 +6405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121597797</v>
+        <v>121598801</v>
       </c>
       <c r="B46" t="n">
-        <v>91411</v>
+        <v>57373</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6401,43 +6417,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506488</v>
+        <v>506390</v>
       </c>
       <c r="R46" t="n">
-        <v>7053023</v>
+        <v>7053088</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6521,10 +6537,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121599680</v>
+        <v>121597320</v>
       </c>
       <c r="B47" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6533,43 +6549,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506380</v>
+        <v>506606</v>
       </c>
       <c r="R47" t="n">
-        <v>7053232</v>
+        <v>7053294</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6604,6 +6625,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6620,22 +6646,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6653,10 +6679,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121599490</v>
+        <v>121597044</v>
       </c>
       <c r="B48" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6665,43 +6691,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506379</v>
+        <v>506743</v>
       </c>
       <c r="R48" t="n">
-        <v>7053186</v>
+        <v>7053366</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,31 +6765,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6785,10 +6781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601508</v>
+        <v>121598549</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6801,37 +6797,51 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506490</v>
+        <v>506432</v>
       </c>
       <c r="R49" t="n">
-        <v>7053371</v>
+        <v>7053087</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6875,26 +6885,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6912,7 +6902,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121597940</v>
+        <v>121599490</v>
       </c>
       <c r="B50" t="n">
         <v>79697</v>
@@ -6946,16 +6936,21 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506473</v>
+        <v>506379</v>
       </c>
       <c r="R50" t="n">
-        <v>7053034</v>
+        <v>7053186</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7039,10 +7034,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121597247</v>
+        <v>121597523</v>
       </c>
       <c r="B51" t="n">
-        <v>90724</v>
+        <v>90746</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7055,21 +7050,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7084,10 +7079,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506669</v>
+        <v>506599</v>
       </c>
       <c r="R51" t="n">
-        <v>7053308</v>
+        <v>7053253</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7148,12 +7143,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7171,10 +7166,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598608</v>
+        <v>121596987</v>
       </c>
       <c r="B52" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7183,51 +7178,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506426</v>
+        <v>506796</v>
       </c>
       <c r="R52" t="n">
-        <v>7053063</v>
+        <v>7053411</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7259,11 +7244,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7276,6 +7256,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7293,10 +7293,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121598834</v>
+        <v>121601872</v>
       </c>
       <c r="B53" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7309,41 +7309,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7352,10 +7338,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506403</v>
+        <v>506612</v>
       </c>
       <c r="R53" t="n">
-        <v>7053127</v>
+        <v>7053395</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7402,6 +7388,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7419,10 +7425,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121597690</v>
+        <v>121598834</v>
       </c>
       <c r="B54" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7435,27 +7441,36 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7469,10 +7484,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506558</v>
+        <v>506403</v>
       </c>
       <c r="R54" t="n">
-        <v>7053116</v>
+        <v>7053127</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7519,26 +7534,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7556,10 +7551,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121596987</v>
+        <v>121598953</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7572,37 +7567,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506796</v>
+        <v>506336</v>
       </c>
       <c r="R55" t="n">
-        <v>7053411</v>
+        <v>7053124</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121597364</v>
+        <v>121597218</v>
       </c>
       <c r="B56" t="n">
-        <v>57357</v>
+        <v>55959</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7699,21 +7699,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7724,21 +7724,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506602</v>
+        <v>506667</v>
       </c>
       <c r="R56" t="n">
-        <v>7053286</v>
+        <v>7053309</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7773,11 +7769,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7786,36 +7777,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7832,10 +7793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121597218</v>
+        <v>121597364</v>
       </c>
       <c r="B57" t="n">
-        <v>55959</v>
+        <v>57357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7848,21 +7809,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7873,17 +7834,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506667</v>
+        <v>506602</v>
       </c>
       <c r="R57" t="n">
-        <v>7053309</v>
+        <v>7053286</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7918,6 +7883,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7926,6 +7896,36 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2579,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597382</v>
+        <v>121598985</v>
       </c>
       <c r="B17" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2595,39 +2595,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506600</v>
+        <v>506335</v>
       </c>
       <c r="R17" t="n">
-        <v>7053289</v>
+        <v>7053140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2688,12 +2693,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2711,10 +2716,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121598985</v>
+        <v>121597382</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2727,44 +2732,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506335</v>
+        <v>506600</v>
       </c>
       <c r="R18" t="n">
-        <v>7053140</v>
+        <v>7053289</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121601357</v>
+        <v>121598902</v>
       </c>
       <c r="B19" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2864,31 +2864,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2902,13 +2898,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506460</v>
+        <v>506352</v>
       </c>
       <c r="R19" t="n">
-        <v>7053365</v>
+        <v>7053112</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2952,6 +2948,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2969,10 +2985,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597990</v>
+        <v>121601357</v>
       </c>
       <c r="B20" t="n">
-        <v>79732</v>
+        <v>57510</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2981,46 +2997,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506470</v>
+        <v>506460</v>
       </c>
       <c r="R20" t="n">
-        <v>7053032</v>
+        <v>7053365</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3064,26 +3089,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3101,10 +3106,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121598902</v>
+        <v>121597990</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>79732</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3113,48 +3118,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506352</v>
+        <v>506470</v>
       </c>
       <c r="R21" t="n">
-        <v>7053112</v>
+        <v>7053032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,22 +3205,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601508</v>
+        <v>121602116</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4031,34 +4031,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506490</v>
+        <v>506843</v>
       </c>
       <c r="R28" t="n">
-        <v>7053371</v>
+        <v>7053491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4119,12 +4124,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4142,10 +4147,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121602116</v>
+        <v>121601508</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4158,39 +4163,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506843</v>
+        <v>506490</v>
       </c>
       <c r="R29" t="n">
-        <v>7053491</v>
+        <v>7053371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121601957</v>
+        <v>121597247</v>
       </c>
       <c r="B37" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506684</v>
+        <v>506669</v>
       </c>
       <c r="R37" t="n">
-        <v>7053378</v>
+        <v>7053308</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5327,12 +5327,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601888</v>
+        <v>121601957</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5366,34 +5366,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506625</v>
+        <v>506684</v>
       </c>
       <c r="R38" t="n">
-        <v>7053387</v>
+        <v>7053378</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5454,12 +5459,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5477,7 +5482,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601859</v>
+        <v>121601888</v>
       </c>
       <c r="B39" t="n">
         <v>78616</v>
@@ -5517,10 +5522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506600</v>
+        <v>506625</v>
       </c>
       <c r="R39" t="n">
-        <v>7053390</v>
+        <v>7053387</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5604,10 +5609,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597247</v>
+        <v>121601859</v>
       </c>
       <c r="B40" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5620,39 +5625,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506669</v>
+        <v>506600</v>
       </c>
       <c r="R40" t="n">
-        <v>7053308</v>
+        <v>7053390</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5713,12 +5713,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121601347</v>
+        <v>121597096</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6030,34 +6030,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506473</v>
+        <v>506735</v>
       </c>
       <c r="R43" t="n">
-        <v>7053383</v>
+        <v>7053336</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6118,12 +6123,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6141,10 +6146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121601916</v>
+        <v>121598801</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6157,34 +6162,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506663</v>
+        <v>506390</v>
       </c>
       <c r="R44" t="n">
-        <v>7053393</v>
+        <v>7053088</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6219,11 +6229,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6250,12 +6255,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6273,10 +6278,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121597096</v>
+        <v>121597320</v>
       </c>
       <c r="B45" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6289,39 +6294,44 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506735</v>
+        <v>506606</v>
       </c>
       <c r="R45" t="n">
-        <v>7053336</v>
+        <v>7053294</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,6 +6366,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6382,12 +6397,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6405,10 +6420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121598801</v>
+        <v>121601347</v>
       </c>
       <c r="B46" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6421,39 +6436,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506390</v>
+        <v>506473</v>
       </c>
       <c r="R46" t="n">
-        <v>7053088</v>
+        <v>7053383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6514,12 +6524,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6537,10 +6547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121597320</v>
+        <v>121601916</v>
       </c>
       <c r="B47" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6553,44 +6563,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506606</v>
+        <v>506663</v>
       </c>
       <c r="R47" t="n">
-        <v>7053294</v>
+        <v>7053393</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>På flertalet granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121601665</v>
+        <v>121601171</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,34 +2082,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506512</v>
+        <v>506381</v>
       </c>
       <c r="R13" t="n">
-        <v>7053384</v>
+        <v>7053357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2170,12 +2175,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2193,10 +2198,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121598608</v>
+        <v>121601357</v>
       </c>
       <c r="B14" t="n">
-        <v>97067</v>
+        <v>57510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2205,31 +2210,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2239,17 +2248,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506426</v>
+        <v>506460</v>
       </c>
       <c r="R14" t="n">
-        <v>7053063</v>
+        <v>7053365</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2279,11 +2288,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2315,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121601171</v>
+        <v>121597940</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,39 +2335,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506381</v>
+        <v>506473</v>
       </c>
       <c r="R15" t="n">
-        <v>7053357</v>
+        <v>7053034</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2414,22 +2413,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2447,10 +2446,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121599680</v>
+        <v>121597408</v>
       </c>
       <c r="B16" t="n">
-        <v>79726</v>
+        <v>91411</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2463,39 +2462,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506380</v>
+        <v>506592</v>
       </c>
       <c r="R16" t="n">
-        <v>7053232</v>
+        <v>7053288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2546,22 +2545,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2579,7 +2578,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121598985</v>
+        <v>121598902</v>
       </c>
       <c r="B17" t="n">
         <v>57373</v>
@@ -2629,10 +2628,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506335</v>
+        <v>506352</v>
       </c>
       <c r="R17" t="n">
-        <v>7053140</v>
+        <v>7053112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2716,10 +2715,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597382</v>
+        <v>121599490</v>
       </c>
       <c r="B18" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2732,39 +2731,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506600</v>
+        <v>506379</v>
       </c>
       <c r="R18" t="n">
-        <v>7053289</v>
+        <v>7053186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2815,22 +2814,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2848,10 +2847,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121598902</v>
+        <v>121598773</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2864,44 +2863,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506352</v>
+        <v>506378</v>
       </c>
       <c r="R19" t="n">
-        <v>7053112</v>
+        <v>7053113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2962,12 +2956,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2985,10 +2979,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121601357</v>
+        <v>121597673</v>
       </c>
       <c r="B20" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3001,31 +2995,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3039,13 +3029,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506460</v>
+        <v>506553</v>
       </c>
       <c r="R20" t="n">
-        <v>7053365</v>
+        <v>7053113</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3089,6 +3079,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3106,10 +3116,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597990</v>
+        <v>121599143</v>
       </c>
       <c r="B21" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3118,20 +3128,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3140,21 +3150,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506470</v>
+        <v>506325</v>
       </c>
       <c r="R21" t="n">
-        <v>7053032</v>
+        <v>7053209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,22 +3210,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3238,10 +3243,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121602039</v>
+        <v>121602116</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3254,34 +3259,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506765</v>
+        <v>506843</v>
       </c>
       <c r="R22" t="n">
-        <v>7053438</v>
+        <v>7053491</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3342,12 +3352,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3365,10 +3375,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597408</v>
+        <v>121601888</v>
       </c>
       <c r="B23" t="n">
-        <v>91411</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3377,43 +3387,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506592</v>
+        <v>506625</v>
       </c>
       <c r="R23" t="n">
-        <v>7053288</v>
+        <v>7053387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3474,12 +3479,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3497,10 +3502,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597940</v>
+        <v>121599680</v>
       </c>
       <c r="B24" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3509,38 +3514,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506473</v>
+        <v>506380</v>
       </c>
       <c r="R24" t="n">
-        <v>7053034</v>
+        <v>7053232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3624,10 +3634,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121599094</v>
+        <v>121597247</v>
       </c>
       <c r="B25" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3640,39 +3650,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506328</v>
+        <v>506669</v>
       </c>
       <c r="R25" t="n">
-        <v>7053195</v>
+        <v>7053308</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3723,22 +3733,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3756,7 +3766,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121599143</v>
+        <v>121601665</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3792,14 +3802,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506325</v>
+        <v>506512</v>
       </c>
       <c r="R26" t="n">
-        <v>7053209</v>
+        <v>7053384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3883,10 +3893,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597978</v>
+        <v>121597320</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3895,43 +3905,48 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506470</v>
+        <v>506606</v>
       </c>
       <c r="R27" t="n">
-        <v>7053032</v>
+        <v>7053294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3966,6 +3981,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3982,22 +4002,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4015,7 +4035,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121602116</v>
+        <v>121598953</v>
       </c>
       <c r="B28" t="n">
         <v>90728</v>
@@ -4056,14 +4076,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506843</v>
+        <v>506336</v>
       </c>
       <c r="R28" t="n">
-        <v>7053491</v>
+        <v>7053124</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4147,10 +4167,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121601508</v>
+        <v>121597523</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4163,34 +4183,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506490</v>
+        <v>506599</v>
       </c>
       <c r="R29" t="n">
-        <v>7053371</v>
+        <v>7053253</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4251,12 +4276,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4274,10 +4299,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121598719</v>
+        <v>121601916</v>
       </c>
       <c r="B30" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4290,44 +4315,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506374</v>
+        <v>506663</v>
       </c>
       <c r="R30" t="n">
-        <v>7053093</v>
+        <v>7053393</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4362,6 +4377,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4388,12 +4408,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4411,7 +4431,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121596964</v>
+        <v>121601859</v>
       </c>
       <c r="B31" t="n">
         <v>78616</v>
@@ -4451,10 +4471,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506818</v>
+        <v>506600</v>
       </c>
       <c r="R31" t="n">
-        <v>7053423</v>
+        <v>7053390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4538,7 +4558,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597690</v>
+        <v>121598719</v>
       </c>
       <c r="B32" t="n">
         <v>57373</v>
@@ -4588,10 +4608,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506558</v>
+        <v>506374</v>
       </c>
       <c r="R32" t="n">
-        <v>7053116</v>
+        <v>7053093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4652,12 +4672,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4675,10 +4695,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597673</v>
+        <v>121597978</v>
       </c>
       <c r="B33" t="n">
-        <v>57373</v>
+        <v>79726</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4687,48 +4707,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506553</v>
+        <v>506470</v>
       </c>
       <c r="R33" t="n">
-        <v>7053113</v>
+        <v>7053032</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4779,22 +4794,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4812,10 +4827,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597306</v>
+        <v>121597130</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4828,16 +4843,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4862,10 +4877,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506628</v>
+        <v>506703</v>
       </c>
       <c r="R34" t="n">
-        <v>7053277</v>
+        <v>7053305</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4898,11 +4913,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4954,10 +4964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597797</v>
+        <v>121598985</v>
       </c>
       <c r="B35" t="n">
-        <v>91411</v>
+        <v>57373</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4966,43 +4976,48 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506488</v>
+        <v>506335</v>
       </c>
       <c r="R35" t="n">
-        <v>7053023</v>
+        <v>7053140</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5086,10 +5101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121598773</v>
+        <v>121597382</v>
       </c>
       <c r="B36" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5102,21 +5117,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5127,14 +5142,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506378</v>
+        <v>506600</v>
       </c>
       <c r="R36" t="n">
-        <v>7053113</v>
+        <v>7053289</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5195,12 +5210,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5218,10 +5233,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597247</v>
+        <v>121599094</v>
       </c>
       <c r="B37" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5234,39 +5249,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506669</v>
+        <v>506328</v>
       </c>
       <c r="R37" t="n">
-        <v>7053308</v>
+        <v>7053195</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5317,22 +5332,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5350,10 +5365,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601957</v>
+        <v>121597797</v>
       </c>
       <c r="B38" t="n">
-        <v>90728</v>
+        <v>91411</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5362,25 +5377,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5395,10 +5410,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506684</v>
+        <v>506488</v>
       </c>
       <c r="R38" t="n">
-        <v>7053378</v>
+        <v>7053023</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5459,12 +5474,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5482,10 +5497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601888</v>
+        <v>121597096</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5498,34 +5513,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506625</v>
+        <v>506735</v>
       </c>
       <c r="R39" t="n">
-        <v>7053387</v>
+        <v>7053336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5586,12 +5606,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5609,10 +5629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121601859</v>
+        <v>121597306</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5625,34 +5645,44 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506600</v>
+        <v>506628</v>
       </c>
       <c r="R40" t="n">
-        <v>7053390</v>
+        <v>7053277</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5687,6 +5717,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5713,12 +5748,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5736,10 +5771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598813</v>
+        <v>121598834</v>
       </c>
       <c r="B41" t="n">
-        <v>90724</v>
+        <v>57510</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5752,48 +5787,53 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>506403</v>
       </c>
       <c r="R41" t="n">
-        <v>7053116</v>
+        <v>7053127</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5840,26 +5880,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5877,7 +5897,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121597130</v>
+        <v>121601872</v>
       </c>
       <c r="B42" t="n">
         <v>57373</v>
@@ -5913,24 +5933,19 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506703</v>
+        <v>506612</v>
       </c>
       <c r="R42" t="n">
-        <v>7053305</v>
+        <v>7053395</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5991,12 +6006,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6014,10 +6029,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121597096</v>
+        <v>121597990</v>
       </c>
       <c r="B43" t="n">
-        <v>90746</v>
+        <v>79732</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6026,31 +6041,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6059,10 +6074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506735</v>
+        <v>506470</v>
       </c>
       <c r="R43" t="n">
-        <v>7053336</v>
+        <v>7053032</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6113,22 +6128,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6146,10 +6161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598801</v>
+        <v>121596964</v>
       </c>
       <c r="B44" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6162,39 +6177,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506390</v>
+        <v>506818</v>
       </c>
       <c r="R44" t="n">
-        <v>7053088</v>
+        <v>7053423</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6255,12 +6265,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6278,10 +6288,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121597320</v>
+        <v>121598608</v>
       </c>
       <c r="B45" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6290,31 +6300,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6324,14 +6334,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506606</v>
+        <v>506426</v>
       </c>
       <c r="R45" t="n">
-        <v>7053294</v>
+        <v>7053063</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6368,7 +6378,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6383,26 +6393,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6547,10 +6537,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601916</v>
+        <v>121601957</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6563,34 +6553,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506663</v>
+        <v>506684</v>
       </c>
       <c r="R47" t="n">
-        <v>7053393</v>
+        <v>7053378</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6625,11 +6620,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6656,12 +6646,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6679,10 +6669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121597044</v>
+        <v>121602039</v>
       </c>
       <c r="B48" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6691,25 +6681,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6719,10 +6709,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506743</v>
+        <v>506765</v>
       </c>
       <c r="R48" t="n">
-        <v>7053366</v>
+        <v>7053438</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6765,6 +6755,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6781,10 +6796,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598549</v>
+        <v>121598813</v>
       </c>
       <c r="B49" t="n">
-        <v>57510</v>
+        <v>90724</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6797,51 +6812,51 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506432</v>
+        <v>506403</v>
       </c>
       <c r="R49" t="n">
-        <v>7053087</v>
+        <v>7053116</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6885,6 +6900,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6902,10 +6937,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121599490</v>
+        <v>121598801</v>
       </c>
       <c r="B50" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6918,39 +6953,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506379</v>
+        <v>506390</v>
       </c>
       <c r="R50" t="n">
-        <v>7053186</v>
+        <v>7053088</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7001,22 +7036,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7034,10 +7069,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121597523</v>
+        <v>121596987</v>
       </c>
       <c r="B51" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7050,42 +7085,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506599</v>
+        <v>506796</v>
       </c>
       <c r="R51" t="n">
-        <v>7053253</v>
+        <v>7053411</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7143,12 +7173,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7166,10 +7196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121596987</v>
+        <v>121597690</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7182,37 +7212,47 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506796</v>
+        <v>506558</v>
       </c>
       <c r="R52" t="n">
-        <v>7053411</v>
+        <v>7053116</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7270,12 +7310,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7293,10 +7333,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121601872</v>
+        <v>121598549</v>
       </c>
       <c r="B53" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7309,27 +7349,36 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7338,13 +7387,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506612</v>
+        <v>506432</v>
       </c>
       <c r="R53" t="n">
-        <v>7053395</v>
+        <v>7053087</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7388,26 +7437,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7425,10 +7454,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121598834</v>
+        <v>121597044</v>
       </c>
       <c r="B54" t="n">
-        <v>57510</v>
+        <v>97067</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7437,57 +7466,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506403</v>
+        <v>506743</v>
       </c>
       <c r="R54" t="n">
-        <v>7053127</v>
+        <v>7053366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7530,11 +7540,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7551,10 +7556,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121598953</v>
+        <v>121601508</v>
       </c>
       <c r="B55" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7567,39 +7572,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506336</v>
+        <v>506490</v>
       </c>
       <c r="R55" t="n">
-        <v>7053124</v>
+        <v>7053371</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2979,10 +2979,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597673</v>
+        <v>121599143</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2995,44 +2995,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506553</v>
+        <v>506325</v>
       </c>
       <c r="R20" t="n">
-        <v>7053113</v>
+        <v>7053209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3093,12 +3083,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3116,10 +3106,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121599143</v>
+        <v>121597673</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3132,34 +3122,44 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506325</v>
+        <v>506553</v>
       </c>
       <c r="R21" t="n">
-        <v>7053209</v>
+        <v>7053113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4827,7 +4827,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597130</v>
+        <v>121598985</v>
       </c>
       <c r="B34" t="n">
         <v>57373</v>
@@ -4863,7 +4863,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506703</v>
+        <v>506335</v>
       </c>
       <c r="R34" t="n">
-        <v>7053305</v>
+        <v>7053140</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121598985</v>
+        <v>121597130</v>
       </c>
       <c r="B35" t="n">
         <v>57373</v>
@@ -5000,7 +5000,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5010,14 +5010,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506335</v>
+        <v>506703</v>
       </c>
       <c r="R35" t="n">
-        <v>7053140</v>
+        <v>7053305</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5078,12 +5078,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597382</v>
+        <v>121597797</v>
       </c>
       <c r="B36" t="n">
-        <v>90724</v>
+        <v>91411</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5113,25 +5113,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506600</v>
+        <v>506488</v>
       </c>
       <c r="R36" t="n">
-        <v>7053289</v>
+        <v>7053023</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121599094</v>
+        <v>121597382</v>
       </c>
       <c r="B37" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5249,39 +5249,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506328</v>
+        <v>506600</v>
       </c>
       <c r="R37" t="n">
-        <v>7053195</v>
+        <v>7053289</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5332,22 +5332,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597797</v>
+        <v>121599094</v>
       </c>
       <c r="B38" t="n">
-        <v>91411</v>
+        <v>79697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5377,43 +5377,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506488</v>
+        <v>506328</v>
       </c>
       <c r="R38" t="n">
-        <v>7053023</v>
+        <v>7053195</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5464,22 +5464,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597306</v>
+        <v>121598834</v>
       </c>
       <c r="B40" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5645,27 +5645,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5675,14 +5684,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506628</v>
+        <v>506403</v>
       </c>
       <c r="R40" t="n">
-        <v>7053277</v>
+        <v>7053127</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5717,11 +5726,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5734,26 +5738,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5771,10 +5755,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598834</v>
+        <v>121597306</v>
       </c>
       <c r="B41" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5787,36 +5771,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5826,14 +5801,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506403</v>
+        <v>506628</v>
       </c>
       <c r="R41" t="n">
-        <v>7053127</v>
+        <v>7053277</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5868,6 +5843,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5880,6 +5860,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121601872</v>
+        <v>121596964</v>
       </c>
       <c r="B42" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5913,39 +5913,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506612</v>
+        <v>506818</v>
       </c>
       <c r="R42" t="n">
-        <v>7053395</v>
+        <v>7053423</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6006,12 +6001,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6029,10 +6024,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121597990</v>
+        <v>121601872</v>
       </c>
       <c r="B43" t="n">
-        <v>79732</v>
+        <v>57373</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6041,43 +6036,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506470</v>
+        <v>506612</v>
       </c>
       <c r="R43" t="n">
-        <v>7053032</v>
+        <v>7053395</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6128,22 +6123,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6161,10 +6156,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121596964</v>
+        <v>121597990</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>79732</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6173,20 +6168,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6195,16 +6190,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506818</v>
+        <v>506470</v>
       </c>
       <c r="R44" t="n">
-        <v>7053423</v>
+        <v>7053032</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6255,22 +6255,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598608</v>
+        <v>121601957</v>
       </c>
       <c r="B45" t="n">
-        <v>97067</v>
+        <v>90728</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6300,48 +6300,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506426</v>
+        <v>506684</v>
       </c>
       <c r="R45" t="n">
-        <v>7053063</v>
+        <v>7053378</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6376,11 +6371,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6393,6 +6383,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6537,10 +6547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601957</v>
+        <v>121598608</v>
       </c>
       <c r="B47" t="n">
-        <v>90728</v>
+        <v>97067</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6549,43 +6559,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506684</v>
+        <v>506426</v>
       </c>
       <c r="R47" t="n">
-        <v>7053378</v>
+        <v>7053063</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,6 +6635,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6632,26 +6652,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121597690</v>
+        <v>121598549</v>
       </c>
       <c r="B52" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7212,27 +7212,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7246,13 +7250,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506558</v>
+        <v>506432</v>
       </c>
       <c r="R52" t="n">
-        <v>7053116</v>
+        <v>7053087</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7296,26 +7300,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7333,10 +7317,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121598549</v>
+        <v>121597690</v>
       </c>
       <c r="B53" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7349,31 +7333,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7387,13 +7367,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506432</v>
+        <v>506558</v>
       </c>
       <c r="R53" t="n">
-        <v>7053087</v>
+        <v>7053116</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7437,6 +7417,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121601171</v>
+        <v>121601916</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,39 +2082,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506381</v>
+        <v>506663</v>
       </c>
       <c r="R13" t="n">
-        <v>7053357</v>
+        <v>7053393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2149,6 +2144,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121601357</v>
+        <v>121598719</v>
       </c>
       <c r="B14" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2214,31 +2214,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2252,13 +2248,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506460</v>
+        <v>506374</v>
       </c>
       <c r="R14" t="n">
-        <v>7053365</v>
+        <v>7053093</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2302,6 +2298,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2319,10 +2335,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597940</v>
+        <v>121598608</v>
       </c>
       <c r="B15" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,38 +2347,48 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506473</v>
+        <v>506426</v>
       </c>
       <c r="R15" t="n">
-        <v>7053034</v>
+        <v>7053063</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2397,6 +2423,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2409,26 +2440,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2446,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597408</v>
+        <v>121599094</v>
       </c>
       <c r="B16" t="n">
-        <v>91411</v>
+        <v>79697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2458,43 +2469,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506592</v>
+        <v>506328</v>
       </c>
       <c r="R16" t="n">
-        <v>7053288</v>
+        <v>7053195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2545,22 +2556,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2578,10 +2589,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121598902</v>
+        <v>121597044</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2590,48 +2601,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506352</v>
+        <v>506743</v>
       </c>
       <c r="R17" t="n">
-        <v>7053112</v>
+        <v>7053366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2674,31 +2675,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2715,10 +2691,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121599490</v>
+        <v>121598549</v>
       </c>
       <c r="B18" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2731,42 +2707,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506379</v>
+        <v>506432</v>
       </c>
       <c r="R18" t="n">
-        <v>7053186</v>
+        <v>7053087</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2810,26 +2795,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2847,7 +2812,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121598773</v>
+        <v>121602116</v>
       </c>
       <c r="B19" t="n">
         <v>90728</v>
@@ -2888,14 +2853,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506378</v>
+        <v>506843</v>
       </c>
       <c r="R19" t="n">
-        <v>7053113</v>
+        <v>7053491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2979,7 +2944,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121599143</v>
+        <v>121596964</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -3015,14 +2980,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506325</v>
+        <v>506818</v>
       </c>
       <c r="R20" t="n">
-        <v>7053209</v>
+        <v>7053423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3106,10 +3071,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597673</v>
+        <v>121596987</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3122,47 +3087,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506553</v>
+        <v>506796</v>
       </c>
       <c r="R21" t="n">
-        <v>7053113</v>
+        <v>7053411</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3220,12 +3175,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3243,10 +3198,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121602116</v>
+        <v>121598834</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>57510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3259,39 +3214,53 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506843</v>
+        <v>506403</v>
       </c>
       <c r="R22" t="n">
-        <v>7053491</v>
+        <v>7053127</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3338,26 +3307,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3375,10 +3324,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601888</v>
+        <v>121598773</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3391,34 +3340,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506625</v>
+        <v>506378</v>
       </c>
       <c r="R23" t="n">
-        <v>7053387</v>
+        <v>7053113</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3479,12 +3433,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3502,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121599680</v>
+        <v>121598813</v>
       </c>
       <c r="B24" t="n">
-        <v>79726</v>
+        <v>90724</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3514,31 +3468,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3547,10 +3510,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506380</v>
+        <v>506403</v>
       </c>
       <c r="R24" t="n">
-        <v>7053232</v>
+        <v>7053116</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3601,22 +3564,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3634,10 +3597,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597247</v>
+        <v>121599490</v>
       </c>
       <c r="B25" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3650,39 +3613,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506669</v>
+        <v>506379</v>
       </c>
       <c r="R25" t="n">
-        <v>7053308</v>
+        <v>7053186</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3733,22 +3696,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3766,7 +3729,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601665</v>
+        <v>121602039</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3806,10 +3769,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506512</v>
+        <v>506765</v>
       </c>
       <c r="R26" t="n">
-        <v>7053384</v>
+        <v>7053438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3893,10 +3856,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597320</v>
+        <v>121601171</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3909,44 +3872,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506606</v>
+        <v>506381</v>
       </c>
       <c r="R27" t="n">
-        <v>7053294</v>
+        <v>7053357</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3981,11 +3939,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4012,12 +3965,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4035,7 +3988,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121598953</v>
+        <v>121601957</v>
       </c>
       <c r="B28" t="n">
         <v>90728</v>
@@ -4076,14 +4029,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506336</v>
+        <v>506684</v>
       </c>
       <c r="R28" t="n">
-        <v>7053124</v>
+        <v>7053378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4167,10 +4120,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597523</v>
+        <v>121597797</v>
       </c>
       <c r="B29" t="n">
-        <v>90746</v>
+        <v>91411</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4179,25 +4132,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4212,10 +4165,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506599</v>
+        <v>506488</v>
       </c>
       <c r="R29" t="n">
-        <v>7053253</v>
+        <v>7053023</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4276,12 +4229,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4299,10 +4252,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601916</v>
+        <v>121601357</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4315,37 +4268,51 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506663</v>
+        <v>506460</v>
       </c>
       <c r="R30" t="n">
-        <v>7053393</v>
+        <v>7053365</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4377,11 +4344,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4394,26 +4356,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4431,10 +4373,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121601859</v>
+        <v>121597382</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4447,24 +4389,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
@@ -4474,7 +4421,7 @@
         <v>506600</v>
       </c>
       <c r="R31" t="n">
-        <v>7053390</v>
+        <v>7053289</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4535,12 +4482,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4558,7 +4505,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121598719</v>
+        <v>121601872</v>
       </c>
       <c r="B32" t="n">
         <v>57373</v>
@@ -4597,21 +4544,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506374</v>
+        <v>506612</v>
       </c>
       <c r="R32" t="n">
-        <v>7053093</v>
+        <v>7053395</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4695,10 +4637,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597978</v>
+        <v>121598985</v>
       </c>
       <c r="B33" t="n">
-        <v>79726</v>
+        <v>57373</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4707,43 +4649,48 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506470</v>
+        <v>506335</v>
       </c>
       <c r="R33" t="n">
-        <v>7053032</v>
+        <v>7053140</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4794,22 +4741,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4827,10 +4774,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121598985</v>
+        <v>121597408</v>
       </c>
       <c r="B34" t="n">
-        <v>57373</v>
+        <v>91411</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4839,48 +4786,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506335</v>
+        <v>506592</v>
       </c>
       <c r="R34" t="n">
-        <v>7053140</v>
+        <v>7053288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,12 +4883,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4964,10 +4906,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597130</v>
+        <v>121601508</v>
       </c>
       <c r="B35" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4980,44 +4922,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506703</v>
+        <v>506490</v>
       </c>
       <c r="R35" t="n">
-        <v>7053305</v>
+        <v>7053371</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5078,12 +5010,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5101,10 +5033,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597797</v>
+        <v>121597940</v>
       </c>
       <c r="B36" t="n">
-        <v>91411</v>
+        <v>79697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5113,43 +5045,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506488</v>
+        <v>506473</v>
       </c>
       <c r="R36" t="n">
-        <v>7053023</v>
+        <v>7053034</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5200,22 +5127,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5233,10 +5160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597382</v>
+        <v>121597306</v>
       </c>
       <c r="B37" t="n">
-        <v>90724</v>
+        <v>57357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5249,27 +5176,32 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5278,10 +5210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506600</v>
+        <v>506628</v>
       </c>
       <c r="R37" t="n">
-        <v>7053289</v>
+        <v>7053277</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5314,6 +5246,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5365,10 +5302,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121599094</v>
+        <v>121601347</v>
       </c>
       <c r="B38" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5381,39 +5318,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506328</v>
+        <v>506473</v>
       </c>
       <c r="R38" t="n">
-        <v>7053195</v>
+        <v>7053383</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5464,22 +5396,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5497,10 +5429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121597096</v>
+        <v>121601859</v>
       </c>
       <c r="B39" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5513,39 +5445,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506735</v>
+        <v>506600</v>
       </c>
       <c r="R39" t="n">
-        <v>7053336</v>
+        <v>7053390</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5606,12 +5533,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5629,10 +5556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598834</v>
+        <v>121597247</v>
       </c>
       <c r="B40" t="n">
-        <v>57510</v>
+        <v>90724</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5645,53 +5572,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506403</v>
+        <v>506669</v>
       </c>
       <c r="R40" t="n">
-        <v>7053127</v>
+        <v>7053308</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5738,6 +5651,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5755,10 +5688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121597306</v>
+        <v>121598902</v>
       </c>
       <c r="B41" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5771,16 +5704,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5791,7 +5724,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5801,14 +5734,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506628</v>
+        <v>506352</v>
       </c>
       <c r="R41" t="n">
-        <v>7053277</v>
+        <v>7053112</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5843,11 +5776,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5874,12 +5802,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5897,7 +5825,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121596964</v>
+        <v>121601665</v>
       </c>
       <c r="B42" t="n">
         <v>78616</v>
@@ -5937,10 +5865,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506818</v>
+        <v>506512</v>
       </c>
       <c r="R42" t="n">
-        <v>7053423</v>
+        <v>7053384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6024,7 +5952,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121601872</v>
+        <v>121598801</v>
       </c>
       <c r="B43" t="n">
         <v>57373</v>
@@ -6069,10 +5997,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506612</v>
+        <v>506390</v>
       </c>
       <c r="R43" t="n">
-        <v>7053395</v>
+        <v>7053088</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6156,10 +6084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121597990</v>
+        <v>121599680</v>
       </c>
       <c r="B44" t="n">
-        <v>79732</v>
+        <v>79726</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6172,39 +6100,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506470</v>
+        <v>506380</v>
       </c>
       <c r="R44" t="n">
-        <v>7053032</v>
+        <v>7053232</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6288,10 +6216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121601957</v>
+        <v>121597990</v>
       </c>
       <c r="B45" t="n">
-        <v>90728</v>
+        <v>79732</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6300,31 +6228,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6333,10 +6261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506684</v>
+        <v>506470</v>
       </c>
       <c r="R45" t="n">
-        <v>7053378</v>
+        <v>7053032</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6387,22 +6315,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6420,10 +6348,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601347</v>
+        <v>121597320</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6436,34 +6364,44 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506473</v>
+        <v>506606</v>
       </c>
       <c r="R46" t="n">
-        <v>7053383</v>
+        <v>7053294</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6498,6 +6436,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6524,12 +6467,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6547,10 +6490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121598608</v>
+        <v>121598953</v>
       </c>
       <c r="B47" t="n">
-        <v>97067</v>
+        <v>90728</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6559,36 +6502,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6597,10 +6535,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506426</v>
+        <v>506336</v>
       </c>
       <c r="R47" t="n">
-        <v>7053063</v>
+        <v>7053124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6635,11 +6573,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6652,6 +6585,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6669,10 +6622,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121602039</v>
+        <v>121597673</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6685,34 +6638,44 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506765</v>
+        <v>506553</v>
       </c>
       <c r="R48" t="n">
-        <v>7053438</v>
+        <v>7053113</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6773,12 +6736,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6796,10 +6759,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598813</v>
+        <v>121601888</v>
       </c>
       <c r="B49" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6812,48 +6775,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506403</v>
+        <v>506625</v>
       </c>
       <c r="R49" t="n">
-        <v>7053116</v>
+        <v>7053387</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6914,12 +6863,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6937,10 +6886,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598801</v>
+        <v>121599143</v>
       </c>
       <c r="B50" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6953,39 +6902,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506390</v>
+        <v>506325</v>
       </c>
       <c r="R50" t="n">
-        <v>7053088</v>
+        <v>7053209</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7046,12 +6990,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7069,10 +7013,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121596987</v>
+        <v>121597690</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7085,37 +7029,47 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506796</v>
+        <v>506558</v>
       </c>
       <c r="R51" t="n">
-        <v>7053411</v>
+        <v>7053116</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7173,12 +7127,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7196,10 +7150,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598549</v>
+        <v>121597096</v>
       </c>
       <c r="B52" t="n">
-        <v>57510</v>
+        <v>90746</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7212,51 +7166,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506432</v>
+        <v>506735</v>
       </c>
       <c r="R52" t="n">
-        <v>7053087</v>
+        <v>7053336</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7300,6 +7245,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7317,10 +7282,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121597690</v>
+        <v>121597523</v>
       </c>
       <c r="B53" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7333,44 +7298,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506558</v>
+        <v>506599</v>
       </c>
       <c r="R53" t="n">
-        <v>7053116</v>
+        <v>7053253</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7431,12 +7391,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7454,10 +7414,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121597044</v>
+        <v>121597978</v>
       </c>
       <c r="B54" t="n">
-        <v>97067</v>
+        <v>79726</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7470,34 +7430,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506743</v>
+        <v>506470</v>
       </c>
       <c r="R54" t="n">
-        <v>7053366</v>
+        <v>7053032</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7540,6 +7505,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7556,10 +7546,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121601508</v>
+        <v>121597130</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7572,34 +7562,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506490</v>
+        <v>506703</v>
       </c>
       <c r="R55" t="n">
-        <v>7053371</v>
+        <v>7053305</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121601916</v>
+        <v>121597690</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,34 +2082,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506663</v>
+        <v>506558</v>
       </c>
       <c r="R13" t="n">
-        <v>7053393</v>
+        <v>7053116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2144,11 +2154,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2175,12 +2180,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2198,7 +2203,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121598719</v>
+        <v>121597130</v>
       </c>
       <c r="B14" t="n">
         <v>57373</v>
@@ -2234,7 +2239,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2244,14 +2249,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506374</v>
+        <v>506703</v>
       </c>
       <c r="R14" t="n">
-        <v>7053093</v>
+        <v>7053305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2312,12 +2317,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2335,10 +2340,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121598608</v>
+        <v>121601508</v>
       </c>
       <c r="B15" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2347,48 +2352,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506426</v>
+        <v>506490</v>
       </c>
       <c r="R15" t="n">
-        <v>7053063</v>
+        <v>7053371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2423,11 +2418,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2440,6 +2430,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2457,10 +2467,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121599094</v>
+        <v>121598813</v>
       </c>
       <c r="B16" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,27 +2483,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2502,10 +2521,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506328</v>
+        <v>506403</v>
       </c>
       <c r="R16" t="n">
-        <v>7053195</v>
+        <v>7053116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2556,22 +2575,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2589,10 +2608,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597044</v>
+        <v>121602039</v>
       </c>
       <c r="B17" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2601,25 +2620,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2629,10 +2648,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506743</v>
+        <v>506765</v>
       </c>
       <c r="R17" t="n">
-        <v>7053366</v>
+        <v>7053438</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2675,6 +2694,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2691,10 +2735,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121598549</v>
+        <v>121596987</v>
       </c>
       <c r="B18" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2707,51 +2751,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506432</v>
+        <v>506796</v>
       </c>
       <c r="R18" t="n">
-        <v>7053087</v>
+        <v>7053411</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2795,6 +2825,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2812,7 +2862,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121602116</v>
+        <v>121601957</v>
       </c>
       <c r="B19" t="n">
         <v>90728</v>
@@ -2857,10 +2907,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506843</v>
+        <v>506684</v>
       </c>
       <c r="R19" t="n">
-        <v>7053491</v>
+        <v>7053378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2944,10 +2994,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596964</v>
+        <v>121597940</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2960,21 +3010,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2984,10 +3034,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506818</v>
+        <v>506473</v>
       </c>
       <c r="R20" t="n">
-        <v>7053423</v>
+        <v>7053034</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3038,22 +3088,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3071,10 +3121,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121596987</v>
+        <v>121599680</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3083,41 +3133,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506796</v>
+        <v>506380</v>
       </c>
       <c r="R21" t="n">
-        <v>7053411</v>
+        <v>7053232</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3165,22 +3220,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3198,10 +3253,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598834</v>
+        <v>121598719</v>
       </c>
       <c r="B22" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3214,36 +3269,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3257,10 +3303,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506403</v>
+        <v>506374</v>
       </c>
       <c r="R22" t="n">
-        <v>7053127</v>
+        <v>7053093</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3307,6 +3353,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3324,10 +3390,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121598773</v>
+        <v>121597673</v>
       </c>
       <c r="B23" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3340,36 +3406,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506378</v>
+        <v>506553</v>
       </c>
       <c r="R23" t="n">
         <v>7053113</v>
@@ -3433,12 +3504,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3456,10 +3527,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121598813</v>
+        <v>121598608</v>
       </c>
       <c r="B24" t="n">
-        <v>90724</v>
+        <v>97067</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3468,40 +3539,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3510,10 +3577,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506403</v>
+        <v>506426</v>
       </c>
       <c r="R24" t="n">
-        <v>7053116</v>
+        <v>7053063</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3548,6 +3615,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3560,26 +3632,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3597,10 +3649,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121599490</v>
+        <v>121597306</v>
       </c>
       <c r="B25" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3613,39 +3665,44 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506379</v>
+        <v>506628</v>
       </c>
       <c r="R25" t="n">
-        <v>7053186</v>
+        <v>7053277</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3680,6 +3737,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3696,22 +3758,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3729,10 +3791,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121602039</v>
+        <v>121597990</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>79732</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3741,20 +3803,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3763,16 +3825,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506765</v>
+        <v>506470</v>
       </c>
       <c r="R26" t="n">
-        <v>7053438</v>
+        <v>7053032</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3823,22 +3890,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3856,10 +3923,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121601171</v>
+        <v>121598801</v>
       </c>
       <c r="B27" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3872,39 +3939,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506381</v>
+        <v>506390</v>
       </c>
       <c r="R27" t="n">
-        <v>7053357</v>
+        <v>7053088</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3965,12 +4032,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3988,10 +4055,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601957</v>
+        <v>121601872</v>
       </c>
       <c r="B28" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4004,39 +4071,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506684</v>
+        <v>506612</v>
       </c>
       <c r="R28" t="n">
-        <v>7053378</v>
+        <v>7053395</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4097,12 +4164,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4120,10 +4187,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597797</v>
+        <v>121601888</v>
       </c>
       <c r="B29" t="n">
-        <v>91411</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4132,43 +4199,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506488</v>
+        <v>506625</v>
       </c>
       <c r="R29" t="n">
-        <v>7053023</v>
+        <v>7053387</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4229,12 +4291,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4252,7 +4314,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601357</v>
+        <v>121598549</v>
       </c>
       <c r="B30" t="n">
         <v>57510</v>
@@ -4287,12 +4349,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4306,13 +4368,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506460</v>
+        <v>506432</v>
       </c>
       <c r="R30" t="n">
-        <v>7053365</v>
+        <v>7053087</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4505,10 +4567,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121601872</v>
+        <v>121599094</v>
       </c>
       <c r="B32" t="n">
-        <v>57373</v>
+        <v>79697</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4521,39 +4583,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506612</v>
+        <v>506328</v>
       </c>
       <c r="R32" t="n">
-        <v>7053395</v>
+        <v>7053195</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4604,22 +4666,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4637,10 +4699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121598985</v>
+        <v>121597797</v>
       </c>
       <c r="B33" t="n">
-        <v>57373</v>
+        <v>91411</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4649,48 +4711,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506335</v>
+        <v>506488</v>
       </c>
       <c r="R33" t="n">
-        <v>7053140</v>
+        <v>7053023</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4774,10 +4831,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597408</v>
+        <v>121599490</v>
       </c>
       <c r="B34" t="n">
-        <v>91411</v>
+        <v>79697</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4786,43 +4843,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506592</v>
+        <v>506379</v>
       </c>
       <c r="R34" t="n">
-        <v>7053288</v>
+        <v>7053186</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4873,22 +4930,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4906,7 +4963,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121601508</v>
+        <v>121601859</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4946,10 +5003,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506490</v>
+        <v>506600</v>
       </c>
       <c r="R35" t="n">
-        <v>7053371</v>
+        <v>7053390</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5033,10 +5090,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597940</v>
+        <v>121597096</v>
       </c>
       <c r="B36" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5049,34 +5106,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506473</v>
+        <v>506735</v>
       </c>
       <c r="R36" t="n">
-        <v>7053034</v>
+        <v>7053336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5127,22 +5189,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5160,10 +5222,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597306</v>
+        <v>121597044</v>
       </c>
       <c r="B37" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5172,48 +5234,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506628</v>
+        <v>506743</v>
       </c>
       <c r="R37" t="n">
-        <v>7053277</v>
+        <v>7053366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5248,11 +5300,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5261,31 +5308,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5302,7 +5324,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601347</v>
+        <v>121601916</v>
       </c>
       <c r="B38" t="n">
         <v>78616</v>
@@ -5338,14 +5360,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506473</v>
+        <v>506663</v>
       </c>
       <c r="R38" t="n">
-        <v>7053383</v>
+        <v>7053393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5378,6 +5400,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5429,10 +5456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601859</v>
+        <v>121597320</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5445,34 +5472,44 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506600</v>
+        <v>506606</v>
       </c>
       <c r="R39" t="n">
-        <v>7053390</v>
+        <v>7053294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5507,6 +5544,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5533,12 +5575,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5556,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597247</v>
+        <v>121598834</v>
       </c>
       <c r="B40" t="n">
-        <v>90724</v>
+        <v>57510</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5572,39 +5614,53 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506669</v>
+        <v>506403</v>
       </c>
       <c r="R40" t="n">
-        <v>7053308</v>
+        <v>7053127</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5651,26 +5707,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5688,10 +5724,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598902</v>
+        <v>121601357</v>
       </c>
       <c r="B41" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5704,27 +5740,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5738,13 +5778,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506352</v>
+        <v>506460</v>
       </c>
       <c r="R41" t="n">
-        <v>7053112</v>
+        <v>7053365</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5788,26 +5828,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5825,10 +5845,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121601665</v>
+        <v>121598773</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5841,34 +5861,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506512</v>
+        <v>506378</v>
       </c>
       <c r="R42" t="n">
-        <v>7053384</v>
+        <v>7053113</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5929,12 +5954,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5952,10 +5977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121598801</v>
+        <v>121599143</v>
       </c>
       <c r="B43" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5968,39 +5993,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506390</v>
+        <v>506325</v>
       </c>
       <c r="R43" t="n">
-        <v>7053088</v>
+        <v>7053209</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6061,12 +6081,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6084,10 +6104,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121599680</v>
+        <v>121597408</v>
       </c>
       <c r="B44" t="n">
-        <v>79726</v>
+        <v>91411</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6100,39 +6120,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506380</v>
+        <v>506592</v>
       </c>
       <c r="R44" t="n">
-        <v>7053232</v>
+        <v>7053288</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6183,22 +6203,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6216,10 +6236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121597990</v>
+        <v>121598902</v>
       </c>
       <c r="B45" t="n">
-        <v>79732</v>
+        <v>57373</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6228,43 +6248,48 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506470</v>
+        <v>506352</v>
       </c>
       <c r="R45" t="n">
-        <v>7053032</v>
+        <v>7053112</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6315,22 +6340,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6348,10 +6373,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121597320</v>
+        <v>121598985</v>
       </c>
       <c r="B46" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6364,16 +6389,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6384,7 +6409,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6398,10 +6423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506606</v>
+        <v>506335</v>
       </c>
       <c r="R46" t="n">
-        <v>7053294</v>
+        <v>7053140</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6436,11 +6461,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6467,12 +6487,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6490,10 +6510,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121598953</v>
+        <v>121601665</v>
       </c>
       <c r="B47" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6506,39 +6526,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506336</v>
+        <v>506512</v>
       </c>
       <c r="R47" t="n">
-        <v>7053124</v>
+        <v>7053384</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6599,12 +6614,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6622,10 +6637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121597673</v>
+        <v>121601347</v>
       </c>
       <c r="B48" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6638,44 +6653,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506553</v>
+        <v>506473</v>
       </c>
       <c r="R48" t="n">
-        <v>7053113</v>
+        <v>7053383</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6736,12 +6741,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6759,10 +6764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601888</v>
+        <v>121601171</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6775,34 +6780,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506625</v>
+        <v>506381</v>
       </c>
       <c r="R49" t="n">
-        <v>7053387</v>
+        <v>7053357</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6863,12 +6873,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6886,10 +6896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121599143</v>
+        <v>121597247</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6902,34 +6912,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506325</v>
+        <v>506669</v>
       </c>
       <c r="R50" t="n">
-        <v>7053209</v>
+        <v>7053308</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6990,12 +7005,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7013,10 +7028,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121597690</v>
+        <v>121596964</v>
       </c>
       <c r="B51" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7029,44 +7044,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506558</v>
+        <v>506818</v>
       </c>
       <c r="R51" t="n">
-        <v>7053116</v>
+        <v>7053423</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7127,12 +7132,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7150,10 +7155,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121597096</v>
+        <v>121602116</v>
       </c>
       <c r="B52" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7166,21 +7171,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7195,10 +7200,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506735</v>
+        <v>506843</v>
       </c>
       <c r="R52" t="n">
-        <v>7053336</v>
+        <v>7053491</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7414,10 +7419,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121597978</v>
+        <v>121598953</v>
       </c>
       <c r="B54" t="n">
-        <v>79726</v>
+        <v>90728</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7426,43 +7431,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506470</v>
+        <v>506336</v>
       </c>
       <c r="R54" t="n">
-        <v>7053032</v>
+        <v>7053124</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7513,22 +7518,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7546,10 +7551,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121597130</v>
+        <v>121597978</v>
       </c>
       <c r="B55" t="n">
-        <v>57373</v>
+        <v>79726</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7558,36 +7563,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506703</v>
+        <v>506470</v>
       </c>
       <c r="R55" t="n">
-        <v>7053305</v>
+        <v>7053032</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7650,22 +7650,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121597218</v>
+        <v>121597364</v>
       </c>
       <c r="B56" t="n">
-        <v>55959</v>
+        <v>57357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7699,21 +7699,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7724,17 +7724,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506667</v>
+        <v>506602</v>
       </c>
       <c r="R56" t="n">
-        <v>7053309</v>
+        <v>7053286</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7769,6 +7773,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7777,6 +7786,36 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7793,10 +7832,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121597364</v>
+        <v>121597218</v>
       </c>
       <c r="B57" t="n">
-        <v>57357</v>
+        <v>55959</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7809,21 +7848,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7834,21 +7873,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506602</v>
+        <v>506667</v>
       </c>
       <c r="R57" t="n">
-        <v>7053286</v>
+        <v>7053309</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7883,11 +7918,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7896,36 +7926,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597690</v>
+        <v>121601859</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,44 +2082,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506558</v>
+        <v>506600</v>
       </c>
       <c r="R13" t="n">
-        <v>7053116</v>
+        <v>7053390</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2180,12 +2170,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2203,7 +2193,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597130</v>
+        <v>121598719</v>
       </c>
       <c r="B14" t="n">
         <v>57373</v>
@@ -2239,7 +2229,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2249,14 +2239,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506703</v>
+        <v>506374</v>
       </c>
       <c r="R14" t="n">
-        <v>7053305</v>
+        <v>7053093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2317,12 +2307,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2340,10 +2330,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121601508</v>
+        <v>121599680</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2352,38 +2342,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506490</v>
+        <v>506380</v>
       </c>
       <c r="R15" t="n">
-        <v>7053371</v>
+        <v>7053232</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2434,22 +2429,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2467,10 +2462,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121598813</v>
+        <v>121597096</v>
       </c>
       <c r="B16" t="n">
-        <v>90724</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2483,33 +2478,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2517,14 +2503,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506403</v>
+        <v>506735</v>
       </c>
       <c r="R16" t="n">
-        <v>7053116</v>
+        <v>7053336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2585,12 +2571,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2735,7 +2721,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596987</v>
+        <v>121601916</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2775,13 +2761,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506796</v>
+        <v>506663</v>
       </c>
       <c r="R18" t="n">
-        <v>7053411</v>
+        <v>7053393</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2811,6 +2797,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2862,10 +2853,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121601957</v>
+        <v>121599490</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2878,39 +2869,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506684</v>
+        <v>506379</v>
       </c>
       <c r="R19" t="n">
-        <v>7053378</v>
+        <v>7053186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2961,22 +2952,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2994,10 +2985,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597940</v>
+        <v>121598549</v>
       </c>
       <c r="B20" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3010,37 +3001,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506473</v>
+        <v>506432</v>
       </c>
       <c r="R20" t="n">
-        <v>7053034</v>
+        <v>7053087</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3084,26 +3089,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3121,10 +3106,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121599680</v>
+        <v>121599094</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3133,31 +3118,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3166,10 +3151,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506380</v>
+        <v>506328</v>
       </c>
       <c r="R21" t="n">
-        <v>7053232</v>
+        <v>7053195</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3253,10 +3238,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598719</v>
+        <v>121602116</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3269,44 +3254,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506374</v>
+        <v>506843</v>
       </c>
       <c r="R22" t="n">
-        <v>7053093</v>
+        <v>7053491</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3367,12 +3347,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3390,10 +3370,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597673</v>
+        <v>121596987</v>
       </c>
       <c r="B23" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3406,47 +3386,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506553</v>
+        <v>506796</v>
       </c>
       <c r="R23" t="n">
-        <v>7053113</v>
+        <v>7053411</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3504,12 +3474,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3527,7 +3497,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121598608</v>
+        <v>121597044</v>
       </c>
       <c r="B24" t="n">
         <v>97067</v>
@@ -3561,26 +3531,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506426</v>
+        <v>506743</v>
       </c>
       <c r="R24" t="n">
-        <v>7053063</v>
+        <v>7053366</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3615,11 +3575,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3628,11 +3583,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3649,10 +3599,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597306</v>
+        <v>121598985</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3665,16 +3615,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3685,7 +3635,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3695,14 +3645,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506628</v>
+        <v>506335</v>
       </c>
       <c r="R25" t="n">
-        <v>7053277</v>
+        <v>7053140</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3737,11 +3687,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3768,12 +3713,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3791,10 +3736,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597990</v>
+        <v>121601665</v>
       </c>
       <c r="B26" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3803,20 +3748,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3825,21 +3770,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506470</v>
+        <v>506512</v>
       </c>
       <c r="R26" t="n">
-        <v>7053032</v>
+        <v>7053384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3890,22 +3830,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3923,10 +3863,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121598801</v>
+        <v>121597320</v>
       </c>
       <c r="B27" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3939,16 +3879,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3959,7 +3899,12 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3968,10 +3913,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506390</v>
+        <v>506606</v>
       </c>
       <c r="R27" t="n">
-        <v>7053088</v>
+        <v>7053294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4006,6 +3951,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4032,12 +3982,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4055,10 +4005,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601872</v>
+        <v>121597408</v>
       </c>
       <c r="B28" t="n">
-        <v>57373</v>
+        <v>91411</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4067,43 +4017,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506612</v>
+        <v>506592</v>
       </c>
       <c r="R28" t="n">
-        <v>7053395</v>
+        <v>7053288</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4164,12 +4114,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4187,10 +4137,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121601888</v>
+        <v>121597247</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4203,34 +4153,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506625</v>
+        <v>506669</v>
       </c>
       <c r="R29" t="n">
-        <v>7053387</v>
+        <v>7053308</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4291,12 +4246,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4314,7 +4269,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121598549</v>
+        <v>121601357</v>
       </c>
       <c r="B30" t="n">
         <v>57510</v>
@@ -4349,12 +4304,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4368,13 +4323,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506432</v>
+        <v>506460</v>
       </c>
       <c r="R30" t="n">
-        <v>7053087</v>
+        <v>7053365</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4435,10 +4390,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597382</v>
+        <v>121598773</v>
       </c>
       <c r="B31" t="n">
-        <v>90724</v>
+        <v>90728</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4451,21 +4406,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4476,14 +4431,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506600</v>
+        <v>506378</v>
       </c>
       <c r="R31" t="n">
-        <v>7053289</v>
+        <v>7053113</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4544,12 +4499,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4567,10 +4522,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121599094</v>
+        <v>121596964</v>
       </c>
       <c r="B32" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4583,39 +4538,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506328</v>
+        <v>506818</v>
       </c>
       <c r="R32" t="n">
-        <v>7053195</v>
+        <v>7053423</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4666,22 +4616,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4699,10 +4649,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597797</v>
+        <v>121597382</v>
       </c>
       <c r="B33" t="n">
-        <v>91411</v>
+        <v>90724</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4711,25 +4661,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4744,10 +4694,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506488</v>
+        <v>506600</v>
       </c>
       <c r="R33" t="n">
-        <v>7053023</v>
+        <v>7053289</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4808,12 +4758,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4831,10 +4781,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121599490</v>
+        <v>121597690</v>
       </c>
       <c r="B34" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4847,39 +4797,44 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506379</v>
+        <v>506558</v>
       </c>
       <c r="R34" t="n">
-        <v>7053186</v>
+        <v>7053116</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4930,22 +4885,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4963,7 +4918,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121601859</v>
+        <v>121601888</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -5003,10 +4958,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506600</v>
+        <v>506625</v>
       </c>
       <c r="R35" t="n">
-        <v>7053390</v>
+        <v>7053387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5090,10 +5045,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597096</v>
+        <v>121597130</v>
       </c>
       <c r="B36" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5106,27 +5061,32 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5135,10 +5095,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506735</v>
+        <v>506703</v>
       </c>
       <c r="R36" t="n">
-        <v>7053336</v>
+        <v>7053305</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5199,12 +5159,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5222,10 +5182,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597044</v>
+        <v>121598953</v>
       </c>
       <c r="B37" t="n">
-        <v>97067</v>
+        <v>90728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5234,38 +5194,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506743</v>
+        <v>506336</v>
       </c>
       <c r="R37" t="n">
-        <v>7053366</v>
+        <v>7053124</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5308,6 +5273,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5324,10 +5314,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601916</v>
+        <v>121601171</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5340,34 +5330,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506663</v>
+        <v>506381</v>
       </c>
       <c r="R38" t="n">
-        <v>7053393</v>
+        <v>7053357</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5402,11 +5397,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5433,12 +5423,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5456,10 +5446,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121597320</v>
+        <v>121597990</v>
       </c>
       <c r="B39" t="n">
-        <v>57357</v>
+        <v>79732</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5468,48 +5458,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506606</v>
+        <v>506470</v>
       </c>
       <c r="R39" t="n">
-        <v>7053294</v>
+        <v>7053032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5544,11 +5529,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5565,22 +5545,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5598,10 +5578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598834</v>
+        <v>121601347</v>
       </c>
       <c r="B40" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5614,53 +5594,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506403</v>
+        <v>506473</v>
       </c>
       <c r="R40" t="n">
-        <v>7053127</v>
+        <v>7053383</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5707,6 +5668,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5724,10 +5705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121601357</v>
+        <v>121601508</v>
       </c>
       <c r="B41" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5740,51 +5721,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506460</v>
+        <v>506490</v>
       </c>
       <c r="R41" t="n">
-        <v>7053365</v>
+        <v>7053371</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5828,6 +5795,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5845,10 +5832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121598773</v>
+        <v>121597306</v>
       </c>
       <c r="B42" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5861,39 +5848,44 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506378</v>
+        <v>506628</v>
       </c>
       <c r="R42" t="n">
-        <v>7053113</v>
+        <v>7053277</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5928,6 +5920,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5954,12 +5951,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6104,10 +6101,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121597408</v>
+        <v>121597940</v>
       </c>
       <c r="B44" t="n">
-        <v>91411</v>
+        <v>79697</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6116,43 +6113,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506592</v>
+        <v>506473</v>
       </c>
       <c r="R44" t="n">
-        <v>7053288</v>
+        <v>7053034</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6203,22 +6195,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6236,10 +6228,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598902</v>
+        <v>121597978</v>
       </c>
       <c r="B45" t="n">
-        <v>57373</v>
+        <v>79726</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6248,48 +6240,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506352</v>
+        <v>506470</v>
       </c>
       <c r="R45" t="n">
-        <v>7053112</v>
+        <v>7053032</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6340,22 +6327,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6373,10 +6360,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121598985</v>
+        <v>121601957</v>
       </c>
       <c r="B46" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6389,44 +6376,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506335</v>
+        <v>506684</v>
       </c>
       <c r="R46" t="n">
-        <v>7053140</v>
+        <v>7053378</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6487,12 +6469,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6510,10 +6492,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601665</v>
+        <v>121598813</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6526,34 +6508,48 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506512</v>
+        <v>506403</v>
       </c>
       <c r="R47" t="n">
-        <v>7053384</v>
+        <v>7053116</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6614,12 +6610,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6637,10 +6633,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121601347</v>
+        <v>121598834</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6653,34 +6649,53 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506473</v>
+        <v>506403</v>
       </c>
       <c r="R48" t="n">
-        <v>7053383</v>
+        <v>7053127</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6727,26 +6742,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6764,10 +6759,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601171</v>
+        <v>121598608</v>
       </c>
       <c r="B49" t="n">
-        <v>90728</v>
+        <v>97067</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6776,31 +6771,36 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506381</v>
+        <v>506426</v>
       </c>
       <c r="R49" t="n">
-        <v>7053357</v>
+        <v>7053063</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6847,6 +6847,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6859,26 +6864,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6896,10 +6881,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121597247</v>
+        <v>121601872</v>
       </c>
       <c r="B50" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6912,39 +6897,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506669</v>
+        <v>506612</v>
       </c>
       <c r="R50" t="n">
-        <v>7053308</v>
+        <v>7053395</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7005,12 +6990,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7028,10 +7013,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121596964</v>
+        <v>121598902</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7044,34 +7029,44 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506818</v>
+        <v>506352</v>
       </c>
       <c r="R51" t="n">
-        <v>7053423</v>
+        <v>7053112</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7132,12 +7127,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7155,10 +7150,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121602116</v>
+        <v>121598801</v>
       </c>
       <c r="B52" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7171,39 +7166,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506843</v>
+        <v>506390</v>
       </c>
       <c r="R52" t="n">
-        <v>7053491</v>
+        <v>7053088</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7264,12 +7259,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7419,10 +7414,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121598953</v>
+        <v>121597673</v>
       </c>
       <c r="B54" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7435,39 +7430,44 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506336</v>
+        <v>506553</v>
       </c>
       <c r="R54" t="n">
-        <v>7053124</v>
+        <v>7053113</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7528,12 +7528,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121597978</v>
+        <v>121597797</v>
       </c>
       <c r="B55" t="n">
-        <v>79726</v>
+        <v>91411</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7567,27 +7567,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506470</v>
+        <v>506488</v>
       </c>
       <c r="R55" t="n">
-        <v>7053032</v>
+        <v>7053023</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7650,22 +7650,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121597364</v>
+        <v>121597218</v>
       </c>
       <c r="B56" t="n">
-        <v>57357</v>
+        <v>55959</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7699,21 +7699,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7724,21 +7724,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506602</v>
+        <v>506667</v>
       </c>
       <c r="R56" t="n">
-        <v>7053286</v>
+        <v>7053309</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7773,11 +7769,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7786,36 +7777,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7832,10 +7793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121597218</v>
+        <v>121597364</v>
       </c>
       <c r="B57" t="n">
-        <v>55959</v>
+        <v>57357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7848,21 +7809,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7873,17 +7834,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506667</v>
+        <v>506602</v>
       </c>
       <c r="R57" t="n">
-        <v>7053309</v>
+        <v>7053286</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7918,6 +7883,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7926,6 +7896,36 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -6633,10 +6633,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121598834</v>
+        <v>121598902</v>
       </c>
       <c r="B48" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6649,36 +6649,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6692,10 +6683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506403</v>
+        <v>506352</v>
       </c>
       <c r="R48" t="n">
-        <v>7053127</v>
+        <v>7053112</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6742,6 +6733,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6759,10 +6770,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598608</v>
+        <v>121598801</v>
       </c>
       <c r="B49" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6771,48 +6782,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506426</v>
+        <v>506390</v>
       </c>
       <c r="R49" t="n">
-        <v>7053063</v>
+        <v>7053088</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6847,11 +6853,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6864,6 +6865,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6881,10 +6902,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121601872</v>
+        <v>121597523</v>
       </c>
       <c r="B50" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6897,39 +6918,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506612</v>
+        <v>506599</v>
       </c>
       <c r="R50" t="n">
-        <v>7053395</v>
+        <v>7053253</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6990,12 +7011,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7013,10 +7034,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121598902</v>
+        <v>121598834</v>
       </c>
       <c r="B51" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7029,27 +7050,36 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7063,10 +7093,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506352</v>
+        <v>506403</v>
       </c>
       <c r="R51" t="n">
-        <v>7053112</v>
+        <v>7053127</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7113,26 +7143,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7150,10 +7160,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598801</v>
+        <v>121598608</v>
       </c>
       <c r="B52" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7162,43 +7172,48 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506390</v>
+        <v>506426</v>
       </c>
       <c r="R52" t="n">
-        <v>7053088</v>
+        <v>7053063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7233,6 +7248,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7245,26 +7265,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7282,10 +7282,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121597523</v>
+        <v>121601872</v>
       </c>
       <c r="B53" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7298,39 +7298,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506599</v>
+        <v>506612</v>
       </c>
       <c r="R53" t="n">
-        <v>7053253</v>
+        <v>7053395</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7391,12 +7391,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2066,7 +2066,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121601859</v>
+        <v>121601347</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -2102,14 +2102,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506600</v>
+        <v>506473</v>
       </c>
       <c r="R13" t="n">
-        <v>7053390</v>
+        <v>7053383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121598719</v>
+        <v>121598834</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2209,27 +2209,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2243,10 +2252,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506374</v>
+        <v>506403</v>
       </c>
       <c r="R14" t="n">
-        <v>7053093</v>
+        <v>7053127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2293,26 +2302,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2330,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121599680</v>
+        <v>121596964</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2342,43 +2331,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506380</v>
+        <v>506818</v>
       </c>
       <c r="R15" t="n">
-        <v>7053232</v>
+        <v>7053423</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,22 +2413,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2462,10 +2446,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597096</v>
+        <v>121597320</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2478,39 +2462,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506735</v>
+        <v>506606</v>
       </c>
       <c r="R16" t="n">
-        <v>7053336</v>
+        <v>7053294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2545,6 +2534,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2571,12 +2565,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2721,10 +2715,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121601916</v>
+        <v>121597690</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2737,34 +2731,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506663</v>
+        <v>506558</v>
       </c>
       <c r="R18" t="n">
-        <v>7053393</v>
+        <v>7053116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2799,11 +2803,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2830,12 +2829,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2985,10 +2984,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121598549</v>
+        <v>121598902</v>
       </c>
       <c r="B20" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3001,31 +3000,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3039,13 +3034,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506432</v>
+        <v>506352</v>
       </c>
       <c r="R20" t="n">
-        <v>7053087</v>
+        <v>7053112</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3089,6 +3084,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3106,10 +3121,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121599094</v>
+        <v>121597797</v>
       </c>
       <c r="B21" t="n">
-        <v>79697</v>
+        <v>91411</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3118,43 +3133,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506328</v>
+        <v>506488</v>
       </c>
       <c r="R21" t="n">
-        <v>7053195</v>
+        <v>7053023</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,22 +3220,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3370,10 +3385,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121596987</v>
+        <v>121598813</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3386,37 +3401,51 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506796</v>
+        <v>506403</v>
       </c>
       <c r="R23" t="n">
-        <v>7053411</v>
+        <v>7053116</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3474,12 +3503,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3497,10 +3526,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597044</v>
+        <v>121601872</v>
       </c>
       <c r="B24" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3509,38 +3538,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506743</v>
+        <v>506612</v>
       </c>
       <c r="R24" t="n">
-        <v>7053366</v>
+        <v>7053395</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3583,6 +3617,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3599,10 +3658,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598985</v>
+        <v>121597523</v>
       </c>
       <c r="B25" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3615,44 +3674,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506335</v>
+        <v>506599</v>
       </c>
       <c r="R25" t="n">
-        <v>7053140</v>
+        <v>7053253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3713,12 +3767,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3736,10 +3790,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601665</v>
+        <v>121601957</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3752,34 +3806,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506512</v>
+        <v>506684</v>
       </c>
       <c r="R26" t="n">
-        <v>7053384</v>
+        <v>7053378</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3840,12 +3899,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3863,10 +3922,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597320</v>
+        <v>121599143</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3879,44 +3938,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506606</v>
+        <v>506325</v>
       </c>
       <c r="R27" t="n">
-        <v>7053294</v>
+        <v>7053209</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3951,11 +4000,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3982,12 +4026,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4005,10 +4049,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597408</v>
+        <v>121601508</v>
       </c>
       <c r="B28" t="n">
-        <v>91411</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4017,43 +4061,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506592</v>
+        <v>506490</v>
       </c>
       <c r="R28" t="n">
-        <v>7053288</v>
+        <v>7053371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4114,12 +4153,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4137,10 +4176,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597247</v>
+        <v>121597673</v>
       </c>
       <c r="B29" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4153,39 +4192,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506669</v>
+        <v>506553</v>
       </c>
       <c r="R29" t="n">
-        <v>7053308</v>
+        <v>7053113</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4246,12 +4290,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4269,10 +4313,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601357</v>
+        <v>121597306</v>
       </c>
       <c r="B30" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4285,31 +4329,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4319,17 +4359,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506460</v>
+        <v>506628</v>
       </c>
       <c r="R30" t="n">
-        <v>7053365</v>
+        <v>7053277</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4361,6 +4401,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4373,6 +4418,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4390,10 +4455,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121598773</v>
+        <v>121598985</v>
       </c>
       <c r="B31" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4406,39 +4471,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506378</v>
+        <v>506335</v>
       </c>
       <c r="R31" t="n">
-        <v>7053113</v>
+        <v>7053140</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4499,12 +4569,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4522,10 +4592,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121596964</v>
+        <v>121598608</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4534,38 +4604,48 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506818</v>
+        <v>506426</v>
       </c>
       <c r="R32" t="n">
-        <v>7053423</v>
+        <v>7053063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4600,6 +4680,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4612,26 +4697,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4649,10 +4714,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597382</v>
+        <v>121597130</v>
       </c>
       <c r="B33" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4665,27 +4730,32 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4694,10 +4764,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506600</v>
+        <v>506703</v>
       </c>
       <c r="R33" t="n">
-        <v>7053289</v>
+        <v>7053305</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4781,10 +4851,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597690</v>
+        <v>121597408</v>
       </c>
       <c r="B34" t="n">
-        <v>57373</v>
+        <v>91411</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4793,48 +4863,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506558</v>
+        <v>506592</v>
       </c>
       <c r="R34" t="n">
-        <v>7053116</v>
+        <v>7053288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4918,10 +4983,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121601888</v>
+        <v>121598953</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4934,34 +4999,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506625</v>
+        <v>506336</v>
       </c>
       <c r="R35" t="n">
-        <v>7053387</v>
+        <v>7053124</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5022,12 +5092,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5045,10 +5115,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597130</v>
+        <v>121597940</v>
       </c>
       <c r="B36" t="n">
-        <v>57373</v>
+        <v>79697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5061,44 +5131,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506703</v>
+        <v>506473</v>
       </c>
       <c r="R36" t="n">
-        <v>7053305</v>
+        <v>7053034</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5149,22 +5209,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5182,10 +5242,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121598953</v>
+        <v>121597096</v>
       </c>
       <c r="B37" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5198,21 +5258,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5223,14 +5283,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506336</v>
+        <v>506735</v>
       </c>
       <c r="R37" t="n">
-        <v>7053124</v>
+        <v>7053336</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5314,10 +5374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601171</v>
+        <v>121599680</v>
       </c>
       <c r="B38" t="n">
-        <v>90728</v>
+        <v>79726</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5326,31 +5386,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5359,10 +5419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506381</v>
+        <v>506380</v>
       </c>
       <c r="R38" t="n">
-        <v>7053357</v>
+        <v>7053232</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5413,22 +5473,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5446,10 +5506,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121597990</v>
+        <v>121598773</v>
       </c>
       <c r="B39" t="n">
-        <v>79732</v>
+        <v>90728</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5458,43 +5518,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506470</v>
+        <v>506378</v>
       </c>
       <c r="R39" t="n">
-        <v>7053032</v>
+        <v>7053113</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5545,22 +5605,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5578,10 +5638,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121601347</v>
+        <v>121597990</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>79732</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5590,20 +5650,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5612,16 +5672,21 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506473</v>
+        <v>506470</v>
       </c>
       <c r="R40" t="n">
-        <v>7053383</v>
+        <v>7053032</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5672,22 +5737,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5705,7 +5770,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121601508</v>
+        <v>121596987</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -5745,13 +5810,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506490</v>
+        <v>506796</v>
       </c>
       <c r="R41" t="n">
-        <v>7053371</v>
+        <v>7053411</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5832,10 +5897,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121597306</v>
+        <v>121601859</v>
       </c>
       <c r="B42" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5848,44 +5913,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506628</v>
+        <v>506600</v>
       </c>
       <c r="R42" t="n">
-        <v>7053277</v>
+        <v>7053390</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5920,11 +5975,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5951,12 +6001,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5974,10 +6024,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121599143</v>
+        <v>121597044</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5986,38 +6036,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506325</v>
+        <v>506743</v>
       </c>
       <c r="R43" t="n">
-        <v>7053209</v>
+        <v>7053366</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6060,31 +6110,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6101,10 +6126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121597940</v>
+        <v>121597978</v>
       </c>
       <c r="B44" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6113,38 +6138,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506473</v>
+        <v>506470</v>
       </c>
       <c r="R44" t="n">
-        <v>7053034</v>
+        <v>7053032</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6228,10 +6258,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121597978</v>
+        <v>121598719</v>
       </c>
       <c r="B45" t="n">
-        <v>79726</v>
+        <v>57373</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6240,43 +6270,48 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506470</v>
+        <v>506374</v>
       </c>
       <c r="R45" t="n">
-        <v>7053032</v>
+        <v>7053093</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6327,22 +6362,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6360,7 +6395,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601957</v>
+        <v>121601171</v>
       </c>
       <c r="B46" t="n">
         <v>90728</v>
@@ -6401,14 +6436,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506684</v>
+        <v>506381</v>
       </c>
       <c r="R46" t="n">
-        <v>7053378</v>
+        <v>7053357</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6492,10 +6527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121598813</v>
+        <v>121601665</v>
       </c>
       <c r="B47" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6508,48 +6543,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506403</v>
+        <v>506512</v>
       </c>
       <c r="R47" t="n">
-        <v>7053116</v>
+        <v>7053384</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6610,12 +6631,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6633,10 +6654,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121598902</v>
+        <v>121601916</v>
       </c>
       <c r="B48" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6649,44 +6670,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506352</v>
+        <v>506663</v>
       </c>
       <c r="R48" t="n">
-        <v>7053112</v>
+        <v>7053393</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6721,6 +6732,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6747,12 +6763,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6770,10 +6786,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598801</v>
+        <v>121597247</v>
       </c>
       <c r="B49" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6786,39 +6802,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506390</v>
+        <v>506669</v>
       </c>
       <c r="R49" t="n">
-        <v>7053088</v>
+        <v>7053308</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6879,12 +6895,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6902,10 +6918,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121597523</v>
+        <v>121601888</v>
       </c>
       <c r="B50" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6918,39 +6934,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506599</v>
+        <v>506625</v>
       </c>
       <c r="R50" t="n">
-        <v>7053253</v>
+        <v>7053387</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7011,12 +7022,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7034,7 +7045,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121598834</v>
+        <v>121601357</v>
       </c>
       <c r="B51" t="n">
         <v>57510</v>
@@ -7072,14 +7083,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7093,13 +7099,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506403</v>
+        <v>506460</v>
       </c>
       <c r="R51" t="n">
-        <v>7053127</v>
+        <v>7053365</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7160,10 +7166,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598608</v>
+        <v>121598801</v>
       </c>
       <c r="B52" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7172,48 +7178,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506426</v>
+        <v>506390</v>
       </c>
       <c r="R52" t="n">
-        <v>7053063</v>
+        <v>7053088</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7248,11 +7249,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7265,6 +7261,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7282,10 +7298,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121601872</v>
+        <v>121598549</v>
       </c>
       <c r="B53" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7298,27 +7314,36 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7327,13 +7352,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506612</v>
+        <v>506432</v>
       </c>
       <c r="R53" t="n">
-        <v>7053395</v>
+        <v>7053087</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7377,26 +7402,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7414,10 +7419,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121597673</v>
+        <v>121597382</v>
       </c>
       <c r="B54" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7430,44 +7435,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506553</v>
+        <v>506600</v>
       </c>
       <c r="R54" t="n">
-        <v>7053113</v>
+        <v>7053289</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121597797</v>
+        <v>121599094</v>
       </c>
       <c r="B55" t="n">
-        <v>91411</v>
+        <v>79697</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7563,43 +7563,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506488</v>
+        <v>506328</v>
       </c>
       <c r="R55" t="n">
-        <v>7053023</v>
+        <v>7053195</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7650,22 +7650,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121597218</v>
+        <v>121597364</v>
       </c>
       <c r="B56" t="n">
-        <v>55959</v>
+        <v>57357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7699,21 +7699,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7724,17 +7724,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506667</v>
+        <v>506602</v>
       </c>
       <c r="R56" t="n">
-        <v>7053309</v>
+        <v>7053286</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7769,6 +7773,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7777,6 +7786,36 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7793,10 +7832,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121597364</v>
+        <v>121597218</v>
       </c>
       <c r="B57" t="n">
-        <v>57357</v>
+        <v>55959</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7809,21 +7848,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7834,21 +7873,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506602</v>
+        <v>506667</v>
       </c>
       <c r="R57" t="n">
-        <v>7053286</v>
+        <v>7053309</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7883,11 +7918,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7896,36 +7926,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Grandominerad skog på hyfsat näringsrik mark med bitvis större mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -3385,10 +3385,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121598813</v>
+        <v>121601872</v>
       </c>
       <c r="B23" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3401,48 +3401,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506403</v>
+        <v>506612</v>
       </c>
       <c r="R23" t="n">
-        <v>7053116</v>
+        <v>7053395</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3526,10 +3517,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601872</v>
+        <v>121598813</v>
       </c>
       <c r="B24" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3542,39 +3533,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506612</v>
+        <v>506403</v>
       </c>
       <c r="R24" t="n">
-        <v>7053395</v>
+        <v>7053116</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597523</v>
+        <v>121599143</v>
       </c>
       <c r="B25" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3674,39 +3674,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506599</v>
+        <v>506325</v>
       </c>
       <c r="R25" t="n">
-        <v>7053253</v>
+        <v>7053209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3767,12 +3762,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3790,10 +3785,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601957</v>
+        <v>121597523</v>
       </c>
       <c r="B26" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3806,21 +3801,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3835,10 +3830,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506684</v>
+        <v>506599</v>
       </c>
       <c r="R26" t="n">
-        <v>7053378</v>
+        <v>7053253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3922,10 +3917,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121599143</v>
+        <v>121601957</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3938,34 +3933,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506325</v>
+        <v>506684</v>
       </c>
       <c r="R27" t="n">
-        <v>7053209</v>
+        <v>7053378</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4313,10 +4313,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597306</v>
+        <v>121598985</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4329,16 +4329,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4349,7 +4349,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4359,14 +4359,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506628</v>
+        <v>506335</v>
       </c>
       <c r="R30" t="n">
-        <v>7053277</v>
+        <v>7053140</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4401,11 +4401,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4432,12 +4427,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4455,10 +4450,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121598985</v>
+        <v>121598608</v>
       </c>
       <c r="B31" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4467,31 +4462,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4501,14 +4496,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506335</v>
+        <v>506426</v>
       </c>
       <c r="R31" t="n">
-        <v>7053140</v>
+        <v>7053063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4543,6 +4538,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4555,26 +4555,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4592,10 +4572,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121598608</v>
+        <v>121597306</v>
       </c>
       <c r="B32" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4604,31 +4584,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4638,14 +4618,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506426</v>
+        <v>506628</v>
       </c>
       <c r="R32" t="n">
-        <v>7053063</v>
+        <v>7053277</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4682,7 +4662,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4697,6 +4677,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2069,7 +2069,7 @@
         <v>121601347</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121598834</v>
+        <v>121601508</v>
       </c>
       <c r="B14" t="n">
-        <v>57510</v>
+        <v>78629</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2209,53 +2209,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506403</v>
+        <v>506490</v>
       </c>
       <c r="R14" t="n">
-        <v>7053127</v>
+        <v>7053371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,6 +2283,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2319,10 +2320,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596964</v>
+        <v>121597990</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>79745</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,20 +2332,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2353,16 +2354,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506818</v>
+        <v>506470</v>
       </c>
       <c r="R15" t="n">
-        <v>7053423</v>
+        <v>7053032</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2413,22 +2419,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2446,10 +2452,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597320</v>
+        <v>121597306</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2492,14 +2498,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506606</v>
+        <v>506628</v>
       </c>
       <c r="R16" t="n">
-        <v>7053294</v>
+        <v>7053277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2588,10 +2594,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121602039</v>
+        <v>121597382</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2604,34 +2610,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506765</v>
+        <v>506600</v>
       </c>
       <c r="R17" t="n">
-        <v>7053438</v>
+        <v>7053289</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2692,12 +2703,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2715,10 +2726,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597690</v>
+        <v>121598953</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>90742</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2731,44 +2742,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506558</v>
+        <v>506336</v>
       </c>
       <c r="R18" t="n">
-        <v>7053116</v>
+        <v>7053124</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2829,12 +2835,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2852,10 +2858,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121599490</v>
+        <v>121598902</v>
       </c>
       <c r="B19" t="n">
-        <v>79697</v>
+        <v>57381</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2868,39 +2874,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506379</v>
+        <v>506352</v>
       </c>
       <c r="R19" t="n">
-        <v>7053186</v>
+        <v>7053112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2951,22 +2962,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2984,10 +2995,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121598902</v>
+        <v>121596964</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3000,44 +3011,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506352</v>
+        <v>506818</v>
       </c>
       <c r="R20" t="n">
-        <v>7053112</v>
+        <v>7053423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3098,12 +3099,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3121,10 +3122,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597797</v>
+        <v>121597690</v>
       </c>
       <c r="B21" t="n">
-        <v>91411</v>
+        <v>57381</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3133,43 +3134,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506488</v>
+        <v>506558</v>
       </c>
       <c r="R21" t="n">
-        <v>7053023</v>
+        <v>7053116</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3230,12 +3236,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3253,10 +3259,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121602116</v>
+        <v>121598985</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>57381</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3269,39 +3275,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506843</v>
+        <v>506335</v>
       </c>
       <c r="R22" t="n">
-        <v>7053491</v>
+        <v>7053140</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3362,12 +3373,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3385,10 +3396,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601872</v>
+        <v>121597797</v>
       </c>
       <c r="B23" t="n">
-        <v>57373</v>
+        <v>91425</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3397,43 +3408,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506612</v>
+        <v>506488</v>
       </c>
       <c r="R23" t="n">
-        <v>7053395</v>
+        <v>7053023</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3517,10 +3528,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121598813</v>
+        <v>121597130</v>
       </c>
       <c r="B24" t="n">
-        <v>90724</v>
+        <v>57381</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3533,48 +3544,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506403</v>
+        <v>506703</v>
       </c>
       <c r="R24" t="n">
-        <v>7053116</v>
+        <v>7053305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3635,12 +3642,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3658,10 +3665,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121599143</v>
+        <v>121601859</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3694,14 +3701,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506325</v>
+        <v>506600</v>
       </c>
       <c r="R25" t="n">
-        <v>7053209</v>
+        <v>7053390</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3785,10 +3792,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597523</v>
+        <v>121597044</v>
       </c>
       <c r="B26" t="n">
-        <v>90746</v>
+        <v>97085</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3797,43 +3804,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506599</v>
+        <v>506743</v>
       </c>
       <c r="R26" t="n">
-        <v>7053253</v>
+        <v>7053366</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3876,31 +3878,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3917,10 +3894,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121601957</v>
+        <v>121597523</v>
       </c>
       <c r="B27" t="n">
-        <v>90728</v>
+        <v>90760</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3933,21 +3910,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3962,10 +3939,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506684</v>
+        <v>506599</v>
       </c>
       <c r="R27" t="n">
-        <v>7053378</v>
+        <v>7053253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4049,10 +4026,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601508</v>
+        <v>121601957</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>90742</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4065,34 +4042,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506490</v>
+        <v>506684</v>
       </c>
       <c r="R28" t="n">
-        <v>7053371</v>
+        <v>7053378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4153,12 +4135,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4176,10 +4158,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597673</v>
+        <v>121602039</v>
       </c>
       <c r="B29" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4192,44 +4174,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506553</v>
+        <v>506765</v>
       </c>
       <c r="R29" t="n">
-        <v>7053113</v>
+        <v>7053438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4290,12 +4262,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4313,10 +4285,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121598985</v>
+        <v>121599490</v>
       </c>
       <c r="B30" t="n">
-        <v>57373</v>
+        <v>79710</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4329,44 +4301,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506335</v>
+        <v>506379</v>
       </c>
       <c r="R30" t="n">
-        <v>7053140</v>
+        <v>7053186</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4417,22 +4384,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4450,10 +4417,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121598608</v>
+        <v>121599680</v>
       </c>
       <c r="B31" t="n">
-        <v>97067</v>
+        <v>79739</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4466,32 +4433,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4500,10 +4462,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506426</v>
+        <v>506380</v>
       </c>
       <c r="R31" t="n">
-        <v>7053063</v>
+        <v>7053232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4538,11 +4500,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4555,6 +4512,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4572,10 +4549,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597306</v>
+        <v>121597978</v>
       </c>
       <c r="B32" t="n">
-        <v>57357</v>
+        <v>79739</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4584,36 +4561,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4622,10 +4594,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506628</v>
+        <v>506470</v>
       </c>
       <c r="R32" t="n">
-        <v>7053277</v>
+        <v>7053032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4660,11 +4632,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4681,22 +4648,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4714,10 +4681,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597130</v>
+        <v>121596987</v>
       </c>
       <c r="B33" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4730,47 +4697,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506703</v>
+        <v>506796</v>
       </c>
       <c r="R33" t="n">
-        <v>7053305</v>
+        <v>7053411</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4828,12 +4785,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4851,10 +4808,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597408</v>
+        <v>121598801</v>
       </c>
       <c r="B34" t="n">
-        <v>91411</v>
+        <v>57381</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4863,43 +4820,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506592</v>
+        <v>506390</v>
       </c>
       <c r="R34" t="n">
-        <v>7053288</v>
+        <v>7053088</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4960,12 +4917,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4983,10 +4940,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121598953</v>
+        <v>121602116</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5024,14 +4981,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506336</v>
+        <v>506843</v>
       </c>
       <c r="R35" t="n">
-        <v>7053124</v>
+        <v>7053491</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5115,10 +5072,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597940</v>
+        <v>121598813</v>
       </c>
       <c r="B36" t="n">
-        <v>79697</v>
+        <v>90738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5131,34 +5088,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506473</v>
+        <v>506403</v>
       </c>
       <c r="R36" t="n">
-        <v>7053034</v>
+        <v>7053116</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5209,22 +5180,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5242,10 +5213,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597096</v>
+        <v>121598773</v>
       </c>
       <c r="B37" t="n">
-        <v>90746</v>
+        <v>90742</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5258,21 +5229,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5283,14 +5254,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506735</v>
+        <v>506378</v>
       </c>
       <c r="R37" t="n">
-        <v>7053336</v>
+        <v>7053113</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5374,10 +5345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121599680</v>
+        <v>121598608</v>
       </c>
       <c r="B38" t="n">
-        <v>79726</v>
+        <v>97085</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5390,27 +5361,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5419,10 +5395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506380</v>
+        <v>506426</v>
       </c>
       <c r="R38" t="n">
-        <v>7053232</v>
+        <v>7053063</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5457,6 +5433,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5469,26 +5450,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5506,10 +5467,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121598773</v>
+        <v>121601872</v>
       </c>
       <c r="B39" t="n">
-        <v>90728</v>
+        <v>57381</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5522,39 +5483,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506378</v>
+        <v>506612</v>
       </c>
       <c r="R39" t="n">
-        <v>7053113</v>
+        <v>7053395</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5615,12 +5576,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5638,10 +5599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597990</v>
+        <v>121597408</v>
       </c>
       <c r="B40" t="n">
-        <v>79732</v>
+        <v>91425</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5654,27 +5615,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5683,10 +5644,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506470</v>
+        <v>506592</v>
       </c>
       <c r="R40" t="n">
-        <v>7053032</v>
+        <v>7053288</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5737,22 +5698,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5770,10 +5731,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121596987</v>
+        <v>121597940</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>79710</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5786,21 +5747,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5810,13 +5771,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506796</v>
+        <v>506473</v>
       </c>
       <c r="R41" t="n">
-        <v>7053411</v>
+        <v>7053034</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5864,22 +5825,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5897,10 +5858,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121601859</v>
+        <v>121598834</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
+        <v>57518</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5913,34 +5874,53 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506600</v>
+        <v>506403</v>
       </c>
       <c r="R42" t="n">
-        <v>7053390</v>
+        <v>7053127</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5987,26 +5967,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6024,10 +5984,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121597044</v>
+        <v>121597247</v>
       </c>
       <c r="B43" t="n">
-        <v>97067</v>
+        <v>90738</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6036,38 +5996,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506743</v>
+        <v>506669</v>
       </c>
       <c r="R43" t="n">
-        <v>7053366</v>
+        <v>7053308</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6110,6 +6075,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6126,10 +6116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121597978</v>
+        <v>121601357</v>
       </c>
       <c r="B44" t="n">
-        <v>79726</v>
+        <v>57518</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6138,46 +6128,55 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506470</v>
+        <v>506460</v>
       </c>
       <c r="R44" t="n">
-        <v>7053032</v>
+        <v>7053365</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6221,26 +6220,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6258,10 +6237,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598719</v>
+        <v>121601665</v>
       </c>
       <c r="B45" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6274,44 +6253,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506374</v>
+        <v>506512</v>
       </c>
       <c r="R45" t="n">
-        <v>7053093</v>
+        <v>7053384</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6372,12 +6341,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6395,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601171</v>
+        <v>121599143</v>
       </c>
       <c r="B46" t="n">
-        <v>90728</v>
+        <v>78629</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6411,39 +6380,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506381</v>
+        <v>506325</v>
       </c>
       <c r="R46" t="n">
-        <v>7053357</v>
+        <v>7053209</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6504,12 +6468,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6527,10 +6491,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601665</v>
+        <v>121598549</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>57518</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6543,37 +6507,51 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506512</v>
+        <v>506432</v>
       </c>
       <c r="R47" t="n">
-        <v>7053384</v>
+        <v>7053087</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6617,26 +6595,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6657,7 +6615,7 @@
         <v>121601916</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6786,10 +6744,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121597247</v>
+        <v>121597320</v>
       </c>
       <c r="B49" t="n">
-        <v>90724</v>
+        <v>57365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6802,39 +6760,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506669</v>
+        <v>506606</v>
       </c>
       <c r="R49" t="n">
-        <v>7053308</v>
+        <v>7053294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6869,6 +6832,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6895,12 +6863,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6918,10 +6886,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121601888</v>
+        <v>121599094</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>79710</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6934,34 +6902,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506625</v>
+        <v>506328</v>
       </c>
       <c r="R50" t="n">
-        <v>7053387</v>
+        <v>7053195</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7012,22 +6985,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7045,10 +7018,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121601357</v>
+        <v>121601888</v>
       </c>
       <c r="B51" t="n">
-        <v>57510</v>
+        <v>78629</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7061,51 +7034,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506460</v>
+        <v>506625</v>
       </c>
       <c r="R51" t="n">
-        <v>7053365</v>
+        <v>7053387</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7149,6 +7108,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7166,10 +7145,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598801</v>
+        <v>121597673</v>
       </c>
       <c r="B52" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7202,7 +7181,12 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7211,10 +7195,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506390</v>
+        <v>506553</v>
       </c>
       <c r="R52" t="n">
-        <v>7053088</v>
+        <v>7053113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7275,12 +7259,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7298,10 +7282,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121598549</v>
+        <v>121598719</v>
       </c>
       <c r="B53" t="n">
-        <v>57510</v>
+        <v>57381</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7314,31 +7298,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7352,13 +7332,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506432</v>
+        <v>506374</v>
       </c>
       <c r="R53" t="n">
-        <v>7053087</v>
+        <v>7053093</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7402,6 +7382,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121597382</v>
+        <v>121597096</v>
       </c>
       <c r="B54" t="n">
-        <v>90724</v>
+        <v>90760</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7435,21 +7435,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506600</v>
+        <v>506735</v>
       </c>
       <c r="R54" t="n">
-        <v>7053289</v>
+        <v>7053336</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7528,12 +7528,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121599094</v>
+        <v>121601171</v>
       </c>
       <c r="B55" t="n">
-        <v>79697</v>
+        <v>90742</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7567,27 +7567,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506328</v>
+        <v>506381</v>
       </c>
       <c r="R55" t="n">
-        <v>7053195</v>
+        <v>7053357</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7650,22 +7650,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7686,7 +7686,7 @@
         <v>121597364</v>
       </c>
       <c r="B56" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>121597218</v>
       </c>
       <c r="B57" t="n">
-        <v>55959</v>
+        <v>55967</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -4417,10 +4417,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121599680</v>
+        <v>121596987</v>
       </c>
       <c r="B31" t="n">
-        <v>79739</v>
+        <v>78629</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4429,46 +4429,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506380</v>
+        <v>506796</v>
       </c>
       <c r="R31" t="n">
-        <v>7053232</v>
+        <v>7053411</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4516,22 +4511,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4549,7 +4544,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597978</v>
+        <v>121599680</v>
       </c>
       <c r="B32" t="n">
         <v>79739</v>
@@ -4590,14 +4585,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506470</v>
+        <v>506380</v>
       </c>
       <c r="R32" t="n">
-        <v>7053032</v>
+        <v>7053232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4681,10 +4676,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121596987</v>
+        <v>121597978</v>
       </c>
       <c r="B33" t="n">
-        <v>78629</v>
+        <v>79739</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4693,41 +4688,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506796</v>
+        <v>506470</v>
       </c>
       <c r="R33" t="n">
-        <v>7053411</v>
+        <v>7053032</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4775,22 +4775,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121598608</v>
+        <v>121597408</v>
       </c>
       <c r="B38" t="n">
-        <v>97085</v>
+        <v>91425</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5361,44 +5361,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506426</v>
+        <v>506592</v>
       </c>
       <c r="R38" t="n">
-        <v>7053063</v>
+        <v>7053288</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5433,11 +5428,6 @@
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5450,6 +5440,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5467,10 +5477,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601872</v>
+        <v>121598608</v>
       </c>
       <c r="B39" t="n">
-        <v>57381</v>
+        <v>97085</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5479,43 +5489,48 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506612</v>
+        <v>506426</v>
       </c>
       <c r="R39" t="n">
-        <v>7053395</v>
+        <v>7053063</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5550,6 +5565,11 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5562,26 +5582,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121597408</v>
+        <v>121601872</v>
       </c>
       <c r="B40" t="n">
-        <v>91425</v>
+        <v>57381</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5611,43 +5611,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Brattmyrarna, Hammerdal, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506592</v>
+        <v>506612</v>
       </c>
       <c r="R40" t="n">
-        <v>7053288</v>
+        <v>7053395</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5708,12 +5708,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 50271-2024 artfynd.xlsx
+++ b/artfynd/A 50271-2024 artfynd.xlsx
@@ -2452,10 +2452,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597306</v>
+        <v>121597382</v>
       </c>
       <c r="B16" t="n">
-        <v>57365</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2468,32 +2468,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2502,10 +2497,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506628</v>
+        <v>506600</v>
       </c>
       <c r="R16" t="n">
-        <v>7053277</v>
+        <v>7053289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2538,11 +2533,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2594,10 +2584,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597382</v>
+        <v>121597306</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>57365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2610,27 +2600,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2639,10 +2634,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506600</v>
+        <v>506628</v>
       </c>
       <c r="R17" t="n">
-        <v>7053289</v>
+        <v>7053277</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2675,6 +2670,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4417,10 +4417,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121596987</v>
+        <v>121599680</v>
       </c>
       <c r="B31" t="n">
-        <v>78629</v>
+        <v>79739</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4429,41 +4429,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506796</v>
+        <v>506380</v>
       </c>
       <c r="R31" t="n">
-        <v>7053411</v>
+        <v>7053232</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4511,22 +4516,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4544,7 +4549,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121599680</v>
+        <v>121597978</v>
       </c>
       <c r="B32" t="n">
         <v>79739</v>
@@ -4585,14 +4590,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Erik-Västlundsbodarna, Erik-Västlundsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506380</v>
+        <v>506470</v>
       </c>
       <c r="R32" t="n">
-        <v>7053232</v>
+        <v>7053032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4676,10 +4681,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597978</v>
+        <v>121596987</v>
       </c>
       <c r="B33" t="n">
-        <v>79739</v>
+        <v>78629</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4688,46 +4693,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506470</v>
+        <v>506796</v>
       </c>
       <c r="R33" t="n">
-        <v>7053032</v>
+        <v>7053411</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4775,22 +4775,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
